--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -3422,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236888</v>
+        <v>113236969</v>
       </c>
       <c r="B28" t="n">
-        <v>78697</v>
+        <v>91290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,25 +3434,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306512</v>
+        <v>306549</v>
       </c>
       <c r="R28" t="n">
-        <v>6523350</v>
+        <v>6523459</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3498,6 +3498,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3524,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236899</v>
+        <v>113236888</v>
       </c>
       <c r="B29" t="n">
-        <v>56765</v>
+        <v>78697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3564,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306499</v>
+        <v>306512</v>
       </c>
       <c r="R29" t="n">
-        <v>6523361</v>
+        <v>6523350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,11 +3605,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236894</v>
+        <v>113236899</v>
       </c>
       <c r="B30" t="n">
-        <v>78697</v>
+        <v>56765</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3647,21 +3647,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306589</v>
+        <v>306499</v>
       </c>
       <c r="R30" t="n">
-        <v>6523489</v>
+        <v>6523361</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,6 +3707,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236969</v>
+        <v>113236894</v>
       </c>
       <c r="B31" t="n">
-        <v>91290</v>
+        <v>78697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3745,25 +3750,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306549</v>
+        <v>306589</v>
       </c>
       <c r="R31" t="n">
-        <v>6523459</v>
+        <v>6523489</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3809,11 +3814,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>113198463</v>
       </c>
       <c r="B4" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198462</v>
+        <v>113198467</v>
       </c>
       <c r="B5" t="n">
-        <v>78697</v>
+        <v>56781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,26 +1029,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306631</v>
+        <v>306536</v>
       </c>
       <c r="R5" t="n">
-        <v>6523391</v>
+        <v>6523466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,13 +1095,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,17 +1117,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113198467</v>
+        <v>113198462</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,27 +1140,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306536</v>
+        <v>306631</v>
       </c>
       <c r="R6" t="n">
-        <v>6523466</v>
+        <v>6523391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,17 +1205,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1233,7 +1233,7 @@
         <v>113198464</v>
       </c>
       <c r="B7" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236876</v>
+        <v>113236877</v>
       </c>
       <c r="B8" t="n">
-        <v>93739</v>
+        <v>93755</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306543</v>
+        <v>306513</v>
       </c>
       <c r="R8" t="n">
-        <v>6523480</v>
+        <v>6523470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236903</v>
+        <v>113236892</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306590</v>
+        <v>306578</v>
       </c>
       <c r="R9" t="n">
-        <v>6523319</v>
+        <v>6523473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,11 +1514,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236916</v>
+        <v>113236913</v>
       </c>
       <c r="B10" t="n">
-        <v>95934</v>
+        <v>96280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306531</v>
+        <v>306509</v>
       </c>
       <c r="R10" t="n">
-        <v>6523473</v>
+        <v>6523355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236968</v>
+        <v>113236909</v>
       </c>
       <c r="B11" t="n">
-        <v>91290</v>
+        <v>56781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1654,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306575</v>
+        <v>306510</v>
       </c>
       <c r="R11" t="n">
-        <v>6523472</v>
+        <v>6523383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1722,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236877</v>
+        <v>113236910</v>
       </c>
       <c r="B12" t="n">
-        <v>93739</v>
+        <v>56781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,25 +1761,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306513</v>
+        <v>306589</v>
       </c>
       <c r="R12" t="n">
-        <v>6523470</v>
+        <v>6523472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,6 +1825,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236911</v>
+        <v>113236883</v>
       </c>
       <c r="B13" t="n">
-        <v>96261</v>
+        <v>78713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306509</v>
+        <v>306515</v>
       </c>
       <c r="R13" t="n">
-        <v>6523483</v>
+        <v>6523326</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,7 +1940,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236925</v>
+        <v>113236967</v>
       </c>
       <c r="B14" t="n">
-        <v>91290</v>
+        <v>91306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306594</v>
+        <v>306533</v>
       </c>
       <c r="R14" t="n">
-        <v>6523469</v>
+        <v>6523475</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,6 +2034,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236907</v>
+        <v>113236886</v>
       </c>
       <c r="B15" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2081,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306479</v>
+        <v>306485</v>
       </c>
       <c r="R15" t="n">
-        <v>6523383</v>
+        <v>6523352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236895</v>
+        <v>113236969</v>
       </c>
       <c r="B16" t="n">
-        <v>78697</v>
+        <v>91306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,25 +2179,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306645</v>
+        <v>306549</v>
       </c>
       <c r="R16" t="n">
-        <v>6523503</v>
+        <v>6523459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,6 +2243,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236887</v>
+        <v>113236927</v>
       </c>
       <c r="B17" t="n">
-        <v>78697</v>
+        <v>94108</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2286,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306511</v>
+        <v>306474</v>
       </c>
       <c r="R17" t="n">
-        <v>6523365</v>
+        <v>6523353</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236909</v>
+        <v>113236890</v>
       </c>
       <c r="B18" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306510</v>
+        <v>306572</v>
       </c>
       <c r="R18" t="n">
-        <v>6523383</v>
+        <v>6523368</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,11 +2452,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236904</v>
+        <v>113236882</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2494,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306627</v>
+        <v>306556</v>
       </c>
       <c r="R19" t="n">
-        <v>6523505</v>
+        <v>6523344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,11 +2554,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2586,10 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236893</v>
+        <v>113236888</v>
       </c>
       <c r="B20" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2626,10 +2620,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306585</v>
+        <v>306512</v>
       </c>
       <c r="R20" t="n">
-        <v>6523469</v>
+        <v>6523350</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236967</v>
+        <v>113236884</v>
       </c>
       <c r="B21" t="n">
-        <v>91290</v>
+        <v>78713</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,25 +2694,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306533</v>
+        <v>306508</v>
       </c>
       <c r="R21" t="n">
-        <v>6523475</v>
+        <v>6523433</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,11 +2758,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236892</v>
+        <v>113236925</v>
       </c>
       <c r="B22" t="n">
-        <v>78697</v>
+        <v>91306</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2796,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306578</v>
+        <v>306594</v>
       </c>
       <c r="R22" t="n">
-        <v>6523473</v>
+        <v>6523469</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,7 +2886,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236896</v>
+        <v>113236899</v>
       </c>
       <c r="B23" t="n">
         <v>56765</v>
@@ -2937,10 +2926,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306488</v>
+        <v>306499</v>
       </c>
       <c r="R23" t="n">
-        <v>6523354</v>
+        <v>6523361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,7 +2993,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236897</v>
+        <v>113236900</v>
       </c>
       <c r="B24" t="n">
         <v>56765</v>
@@ -3044,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306516</v>
+        <v>306496</v>
       </c>
       <c r="R24" t="n">
-        <v>6523349</v>
+        <v>6523360</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236884</v>
+        <v>113236902</v>
       </c>
       <c r="B25" t="n">
-        <v>78697</v>
+        <v>56781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3127,21 +3116,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306508</v>
+        <v>306520</v>
       </c>
       <c r="R25" t="n">
-        <v>6523433</v>
+        <v>6523332</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,6 +3176,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236885</v>
+        <v>113236903</v>
       </c>
       <c r="B26" t="n">
-        <v>78697</v>
+        <v>56781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,21 +3223,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306496</v>
+        <v>306590</v>
       </c>
       <c r="R26" t="n">
-        <v>6523349</v>
+        <v>6523319</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,6 +3283,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,7 +3314,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236898</v>
+        <v>113236896</v>
       </c>
       <c r="B27" t="n">
         <v>56765</v>
@@ -3355,10 +3354,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306506</v>
+        <v>306488</v>
       </c>
       <c r="R27" t="n">
-        <v>6523348</v>
+        <v>6523354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236969</v>
+        <v>113236906</v>
       </c>
       <c r="B28" t="n">
-        <v>91290</v>
+        <v>56781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3434,25 +3433,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306549</v>
+        <v>306644</v>
       </c>
       <c r="R28" t="n">
-        <v>6523459</v>
+        <v>6523374</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3502,7 +3501,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3529,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236888</v>
+        <v>113236893</v>
       </c>
       <c r="B29" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306512</v>
+        <v>306585</v>
       </c>
       <c r="R29" t="n">
-        <v>6523350</v>
+        <v>6523469</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3631,10 +3630,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236899</v>
+        <v>113236907</v>
       </c>
       <c r="B30" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3647,16 +3646,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3671,10 +3670,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306499</v>
+        <v>306479</v>
       </c>
       <c r="R30" t="n">
-        <v>6523361</v>
+        <v>6523383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3711,7 +3710,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3738,10 +3737,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236894</v>
+        <v>113236881</v>
       </c>
       <c r="B31" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3778,10 +3777,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306589</v>
+        <v>306645</v>
       </c>
       <c r="R31" t="n">
-        <v>6523489</v>
+        <v>6523507</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3840,10 +3839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236902</v>
+        <v>113236895</v>
       </c>
       <c r="B32" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,21 +3855,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3879,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306520</v>
+        <v>306645</v>
       </c>
       <c r="R32" t="n">
-        <v>6523332</v>
+        <v>6523503</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3916,11 +3915,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3947,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236913</v>
+        <v>113236904</v>
       </c>
       <c r="B33" t="n">
-        <v>96264</v>
+        <v>56781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3959,25 +3953,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3987,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306509</v>
+        <v>306627</v>
       </c>
       <c r="R33" t="n">
-        <v>6523355</v>
+        <v>6523505</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4023,6 +4017,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4049,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236900</v>
+        <v>113236876</v>
       </c>
       <c r="B34" t="n">
-        <v>56765</v>
+        <v>93755</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4061,25 +4060,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306496</v>
+        <v>306543</v>
       </c>
       <c r="R34" t="n">
-        <v>6523360</v>
+        <v>6523480</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,11 +4124,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4156,10 +4150,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236881</v>
+        <v>113236968</v>
       </c>
       <c r="B35" t="n">
-        <v>78697</v>
+        <v>91306</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4168,25 +4162,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4196,10 +4190,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306645</v>
+        <v>306575</v>
       </c>
       <c r="R35" t="n">
-        <v>6523507</v>
+        <v>6523472</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4232,6 +4226,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,10 +4257,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236908</v>
+        <v>113236897</v>
       </c>
       <c r="B36" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4274,16 +4273,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4298,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306598</v>
+        <v>306516</v>
       </c>
       <c r="R36" t="n">
-        <v>6523398</v>
+        <v>6523349</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4365,10 +4364,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236886</v>
+        <v>113236908</v>
       </c>
       <c r="B37" t="n">
-        <v>78697</v>
+        <v>56781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4381,21 +4380,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4405,10 +4404,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306485</v>
+        <v>306598</v>
       </c>
       <c r="R37" t="n">
-        <v>6523352</v>
+        <v>6523398</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4441,6 +4440,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4467,10 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236926</v>
+        <v>113236891</v>
       </c>
       <c r="B38" t="n">
-        <v>91290</v>
+        <v>78713</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,25 +4483,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306544</v>
+        <v>306571</v>
       </c>
       <c r="R38" t="n">
-        <v>6523404</v>
+        <v>6523493</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236905</v>
+        <v>113236887</v>
       </c>
       <c r="B39" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4585,21 +4589,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4609,10 +4613,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306537</v>
+        <v>306511</v>
       </c>
       <c r="R39" t="n">
-        <v>6523319</v>
+        <v>6523365</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4645,11 +4649,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4676,10 +4675,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236882</v>
+        <v>113236885</v>
       </c>
       <c r="B40" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4716,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306556</v>
+        <v>306496</v>
       </c>
       <c r="R40" t="n">
-        <v>6523344</v>
+        <v>6523349</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,10 +4777,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236891</v>
+        <v>113236894</v>
       </c>
       <c r="B41" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,10 +4817,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306571</v>
+        <v>306589</v>
       </c>
       <c r="R41" t="n">
-        <v>6523493</v>
+        <v>6523489</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4880,10 +4879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236890</v>
+        <v>113236889</v>
       </c>
       <c r="B42" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4920,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306572</v>
+        <v>306547</v>
       </c>
       <c r="R42" t="n">
-        <v>6523368</v>
+        <v>6523388</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4985,7 +4984,7 @@
         <v>113236912</v>
       </c>
       <c r="B43" t="n">
-        <v>91313</v>
+        <v>91329</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5084,10 +5083,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236889</v>
+        <v>113236916</v>
       </c>
       <c r="B44" t="n">
-        <v>78697</v>
+        <v>95950</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,25 +5095,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>2606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5123,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306547</v>
+        <v>306531</v>
       </c>
       <c r="R44" t="n">
-        <v>6523388</v>
+        <v>6523473</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5186,10 +5185,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236883</v>
+        <v>113236926</v>
       </c>
       <c r="B45" t="n">
-        <v>78697</v>
+        <v>91306</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,25 +5197,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5225,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306515</v>
+        <v>306544</v>
       </c>
       <c r="R45" t="n">
-        <v>6523326</v>
+        <v>6523404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5287,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236927</v>
+        <v>113236905</v>
       </c>
       <c r="B46" t="n">
-        <v>94092</v>
+        <v>56781</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5300,25 +5299,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5328,10 +5327,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306474</v>
+        <v>306537</v>
       </c>
       <c r="R46" t="n">
-        <v>6523353</v>
+        <v>6523319</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5364,6 +5363,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,10 +5394,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236906</v>
+        <v>113236898</v>
       </c>
       <c r="B47" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,16 +5410,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5430,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306644</v>
+        <v>306506</v>
       </c>
       <c r="R47" t="n">
-        <v>6523374</v>
+        <v>6523348</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5470,7 +5474,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5501,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236910</v>
+        <v>113236911</v>
       </c>
       <c r="B48" t="n">
-        <v>56781</v>
+        <v>96277</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5513,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306589</v>
+        <v>306509</v>
       </c>
       <c r="R48" t="n">
-        <v>6523472</v>
+        <v>6523483</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5575,17 +5579,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236877</v>
+        <v>113236892</v>
       </c>
       <c r="B8" t="n">
-        <v>93755</v>
+        <v>78713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306513</v>
+        <v>306578</v>
       </c>
       <c r="R8" t="n">
-        <v>6523470</v>
+        <v>6523473</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236892</v>
+        <v>113236877</v>
       </c>
       <c r="B9" t="n">
-        <v>78713</v>
+        <v>93755</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,25 +1450,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306578</v>
+        <v>306513</v>
       </c>
       <c r="R9" t="n">
-        <v>6523473</v>
+        <v>6523470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236927</v>
+        <v>113236890</v>
       </c>
       <c r="B17" t="n">
-        <v>94108</v>
+        <v>78713</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,25 +2286,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306474</v>
+        <v>306572</v>
       </c>
       <c r="R17" t="n">
-        <v>6523353</v>
+        <v>6523368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236890</v>
+        <v>113236882</v>
       </c>
       <c r="B18" t="n">
         <v>78713</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306572</v>
+        <v>306556</v>
       </c>
       <c r="R18" t="n">
-        <v>6523368</v>
+        <v>6523344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236882</v>
+        <v>113236927</v>
       </c>
       <c r="B19" t="n">
-        <v>78713</v>
+        <v>94108</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,25 +2490,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306556</v>
+        <v>306474</v>
       </c>
       <c r="R19" t="n">
-        <v>6523344</v>
+        <v>6523353</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236896</v>
+        <v>113236906</v>
       </c>
       <c r="B27" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306488</v>
+        <v>306644</v>
       </c>
       <c r="R27" t="n">
-        <v>6523354</v>
+        <v>6523374</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236906</v>
+        <v>113236896</v>
       </c>
       <c r="B28" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3437,16 +3437,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306644</v>
+        <v>306488</v>
       </c>
       <c r="R28" t="n">
-        <v>6523374</v>
+        <v>6523354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236893</v>
+        <v>113236907</v>
       </c>
       <c r="B29" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,21 +3544,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3568,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306585</v>
+        <v>306479</v>
       </c>
       <c r="R29" t="n">
-        <v>6523469</v>
+        <v>6523383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,6 +3604,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236907</v>
+        <v>113236893</v>
       </c>
       <c r="B30" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,21 +3651,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3670,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306479</v>
+        <v>306585</v>
       </c>
       <c r="R30" t="n">
-        <v>6523383</v>
+        <v>6523469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3706,11 +3711,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236876</v>
+        <v>113236897</v>
       </c>
       <c r="B34" t="n">
-        <v>93755</v>
+        <v>56765</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306543</v>
+        <v>306516</v>
       </c>
       <c r="R34" t="n">
-        <v>6523480</v>
+        <v>6523349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,6 +4124,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4150,10 +4155,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236968</v>
+        <v>113236876</v>
       </c>
       <c r="B35" t="n">
-        <v>91306</v>
+        <v>93755</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,21 +4171,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2810</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4190,10 +4195,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306575</v>
+        <v>306543</v>
       </c>
       <c r="R35" t="n">
-        <v>6523472</v>
+        <v>6523480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4226,11 +4231,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,10 +4257,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236897</v>
+        <v>113236968</v>
       </c>
       <c r="B36" t="n">
-        <v>56765</v>
+        <v>91306</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4269,25 +4269,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306516</v>
+        <v>306575</v>
       </c>
       <c r="R36" t="n">
-        <v>6523349</v>
+        <v>6523472</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4879,10 +4879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236889</v>
+        <v>113236916</v>
       </c>
       <c r="B42" t="n">
-        <v>78713</v>
+        <v>95950</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,25 +4891,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306547</v>
+        <v>306531</v>
       </c>
       <c r="R42" t="n">
-        <v>6523388</v>
+        <v>6523473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236912</v>
+        <v>113236926</v>
       </c>
       <c r="B43" t="n">
-        <v>91329</v>
+        <v>91306</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,25 +4993,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306536</v>
+        <v>306544</v>
       </c>
       <c r="R43" t="n">
-        <v>6523428</v>
+        <v>6523404</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236916</v>
+        <v>113236889</v>
       </c>
       <c r="B44" t="n">
-        <v>95950</v>
+        <v>78713</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,25 +5095,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306531</v>
+        <v>306547</v>
       </c>
       <c r="R44" t="n">
-        <v>6523473</v>
+        <v>6523388</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236926</v>
+        <v>113236912</v>
       </c>
       <c r="B45" t="n">
-        <v>91306</v>
+        <v>91329</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5197,25 +5197,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5225,10 +5225,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306544</v>
+        <v>306536</v>
       </c>
       <c r="R45" t="n">
-        <v>6523404</v>
+        <v>6523428</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113198463</v>
+        <v>113198467</v>
       </c>
       <c r="B4" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,26 +923,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306553</v>
+        <v>306536</v>
       </c>
       <c r="R4" t="n">
-        <v>6523421</v>
+        <v>6523466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,13 +989,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198467</v>
+        <v>113198462</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,27 +1034,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306536</v>
+        <v>306631</v>
       </c>
       <c r="R5" t="n">
-        <v>6523466</v>
+        <v>6523391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,17 +1099,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,14 +1117,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113198462</v>
+        <v>113198463</v>
       </c>
       <c r="B6" t="n">
         <v>78713</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306631</v>
+        <v>306553</v>
       </c>
       <c r="R6" t="n">
-        <v>6523391</v>
+        <v>6523421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236892</v>
+        <v>113236968</v>
       </c>
       <c r="B8" t="n">
-        <v>78713</v>
+        <v>91306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306578</v>
+        <v>306575</v>
       </c>
       <c r="R8" t="n">
-        <v>6523473</v>
+        <v>6523472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,6 +1412,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236877</v>
+        <v>113236969</v>
       </c>
       <c r="B9" t="n">
-        <v>93755</v>
+        <v>91306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306513</v>
+        <v>306549</v>
       </c>
       <c r="R9" t="n">
-        <v>6523470</v>
+        <v>6523459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1519,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236913</v>
+        <v>113236892</v>
       </c>
       <c r="B10" t="n">
-        <v>96280</v>
+        <v>78713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1562,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306509</v>
+        <v>306578</v>
       </c>
       <c r="R10" t="n">
-        <v>6523355</v>
+        <v>6523473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236909</v>
+        <v>113236877</v>
       </c>
       <c r="B11" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,25 +1664,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306510</v>
+        <v>306513</v>
       </c>
       <c r="R11" t="n">
-        <v>6523383</v>
+        <v>6523470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,11 +1728,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,7 +1754,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236910</v>
+        <v>113236907</v>
       </c>
       <c r="B12" t="n">
         <v>56781</v>
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306589</v>
+        <v>306479</v>
       </c>
       <c r="R12" t="n">
-        <v>6523472</v>
+        <v>6523383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236883</v>
+        <v>113236912</v>
       </c>
       <c r="B13" t="n">
-        <v>78713</v>
+        <v>91329</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306515</v>
+        <v>306536</v>
       </c>
       <c r="R13" t="n">
-        <v>6523326</v>
+        <v>6523428</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236967</v>
+        <v>113236909</v>
       </c>
       <c r="B14" t="n">
-        <v>91306</v>
+        <v>56781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,25 +1975,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306533</v>
+        <v>306510</v>
       </c>
       <c r="R14" t="n">
-        <v>6523475</v>
+        <v>6523383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2043,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,10 +2070,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236886</v>
+        <v>113236908</v>
       </c>
       <c r="B15" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306485</v>
+        <v>306598</v>
       </c>
       <c r="R15" t="n">
-        <v>6523352</v>
+        <v>6523398</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,6 +2146,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2177,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236969</v>
+        <v>113236889</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>78713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2189,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306549</v>
+        <v>306547</v>
       </c>
       <c r="R16" t="n">
-        <v>6523459</v>
+        <v>6523388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,11 +2253,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,7 +2279,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236890</v>
+        <v>113236885</v>
       </c>
       <c r="B17" t="n">
         <v>78713</v>
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306572</v>
+        <v>306496</v>
       </c>
       <c r="R17" t="n">
-        <v>6523368</v>
+        <v>6523349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,7 +2381,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236882</v>
+        <v>113236895</v>
       </c>
       <c r="B18" t="n">
         <v>78713</v>
@@ -2416,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306556</v>
+        <v>306645</v>
       </c>
       <c r="R18" t="n">
-        <v>6523344</v>
+        <v>6523503</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236927</v>
+        <v>113236905</v>
       </c>
       <c r="B19" t="n">
-        <v>94108</v>
+        <v>56781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2518,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306474</v>
+        <v>306537</v>
       </c>
       <c r="R19" t="n">
-        <v>6523353</v>
+        <v>6523319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,6 +2559,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2580,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236888</v>
+        <v>113236967</v>
       </c>
       <c r="B20" t="n">
-        <v>78713</v>
+        <v>91306</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,25 +2602,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2620,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306512</v>
+        <v>306533</v>
       </c>
       <c r="R20" t="n">
-        <v>6523350</v>
+        <v>6523475</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,6 +2666,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2682,7 +2697,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236884</v>
+        <v>113236891</v>
       </c>
       <c r="B21" t="n">
         <v>78713</v>
@@ -2722,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306508</v>
+        <v>306571</v>
       </c>
       <c r="R21" t="n">
-        <v>6523433</v>
+        <v>6523493</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236925</v>
+        <v>113236916</v>
       </c>
       <c r="B22" t="n">
-        <v>91306</v>
+        <v>95950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,21 +2815,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306594</v>
+        <v>306531</v>
       </c>
       <c r="R22" t="n">
-        <v>6523469</v>
+        <v>6523473</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236899</v>
+        <v>113236890</v>
       </c>
       <c r="B23" t="n">
-        <v>56765</v>
+        <v>78713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306499</v>
+        <v>306572</v>
       </c>
       <c r="R23" t="n">
-        <v>6523361</v>
+        <v>6523368</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,11 +2977,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236900</v>
+        <v>113236883</v>
       </c>
       <c r="B24" t="n">
-        <v>56765</v>
+        <v>78713</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3033,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306496</v>
+        <v>306515</v>
       </c>
       <c r="R24" t="n">
-        <v>6523360</v>
+        <v>6523326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,11 +3079,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3100,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236902</v>
+        <v>113236897</v>
       </c>
       <c r="B25" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3116,16 +3121,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3140,10 +3145,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306520</v>
+        <v>306516</v>
       </c>
       <c r="R25" t="n">
-        <v>6523332</v>
+        <v>6523349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3212,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236903</v>
+        <v>113236926</v>
       </c>
       <c r="B26" t="n">
-        <v>56781</v>
+        <v>91306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,25 +3224,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306590</v>
+        <v>306544</v>
       </c>
       <c r="R26" t="n">
-        <v>6523319</v>
+        <v>6523404</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,11 +3288,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236896</v>
+        <v>113236925</v>
       </c>
       <c r="B28" t="n">
-        <v>56765</v>
+        <v>91306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,25 +3433,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306488</v>
+        <v>306594</v>
       </c>
       <c r="R28" t="n">
-        <v>6523354</v>
+        <v>6523469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,11 +3497,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236907</v>
+        <v>113236882</v>
       </c>
       <c r="B29" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,21 +3539,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3568,10 +3563,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306479</v>
+        <v>306556</v>
       </c>
       <c r="R29" t="n">
-        <v>6523383</v>
+        <v>6523344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,11 +3599,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3635,10 +3625,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236893</v>
+        <v>113236902</v>
       </c>
       <c r="B30" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,21 +3641,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3675,10 +3665,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306585</v>
+        <v>306520</v>
       </c>
       <c r="R30" t="n">
-        <v>6523469</v>
+        <v>6523332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3711,6 +3701,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3737,10 +3732,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236881</v>
+        <v>113236913</v>
       </c>
       <c r="B31" t="n">
-        <v>78713</v>
+        <v>96280</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,25 +3744,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3777,10 +3772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306645</v>
+        <v>306509</v>
       </c>
       <c r="R31" t="n">
-        <v>6523507</v>
+        <v>6523355</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,10 +3834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236895</v>
+        <v>113236899</v>
       </c>
       <c r="B32" t="n">
-        <v>78713</v>
+        <v>56765</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3855,21 +3850,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3879,10 +3874,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306645</v>
+        <v>306499</v>
       </c>
       <c r="R32" t="n">
-        <v>6523503</v>
+        <v>6523361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,6 +3910,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236904</v>
+        <v>113236896</v>
       </c>
       <c r="B33" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,16 +3957,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306627</v>
+        <v>306488</v>
       </c>
       <c r="R33" t="n">
-        <v>6523505</v>
+        <v>6523354</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4048,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236897</v>
+        <v>113236911</v>
       </c>
       <c r="B34" t="n">
-        <v>56765</v>
+        <v>96277</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4060,25 +4060,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306516</v>
+        <v>306509</v>
       </c>
       <c r="R34" t="n">
-        <v>6523349</v>
+        <v>6523483</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,17 +4126,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4155,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236876</v>
+        <v>113236886</v>
       </c>
       <c r="B35" t="n">
-        <v>93755</v>
+        <v>78713</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,25 +4163,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4195,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306543</v>
+        <v>306485</v>
       </c>
       <c r="R35" t="n">
-        <v>6523480</v>
+        <v>6523352</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236968</v>
+        <v>113236884</v>
       </c>
       <c r="B36" t="n">
-        <v>91306</v>
+        <v>78713</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4269,25 +4265,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4297,10 +4293,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306575</v>
+        <v>306508</v>
       </c>
       <c r="R36" t="n">
-        <v>6523472</v>
+        <v>6523433</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4333,11 +4329,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,10 +4355,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236908</v>
+        <v>113236876</v>
       </c>
       <c r="B37" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4376,25 +4367,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4404,10 +4395,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306598</v>
+        <v>306543</v>
       </c>
       <c r="R37" t="n">
-        <v>6523398</v>
+        <v>6523480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4440,11 +4431,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4471,10 +4457,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236891</v>
+        <v>113236927</v>
       </c>
       <c r="B38" t="n">
-        <v>78713</v>
+        <v>94108</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,25 +4469,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4497,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306571</v>
+        <v>306474</v>
       </c>
       <c r="R38" t="n">
-        <v>6523493</v>
+        <v>6523353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236887</v>
+        <v>113236904</v>
       </c>
       <c r="B39" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4589,21 +4575,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4613,10 +4599,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306511</v>
+        <v>306627</v>
       </c>
       <c r="R39" t="n">
-        <v>6523365</v>
+        <v>6523505</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4649,6 +4635,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4675,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236885</v>
+        <v>113236903</v>
       </c>
       <c r="B40" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4691,21 +4682,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4715,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306496</v>
+        <v>306590</v>
       </c>
       <c r="R40" t="n">
-        <v>6523349</v>
+        <v>6523319</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,6 +4742,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4777,7 +4773,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236894</v>
+        <v>113236888</v>
       </c>
       <c r="B41" t="n">
         <v>78713</v>
@@ -4817,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306589</v>
+        <v>306512</v>
       </c>
       <c r="R41" t="n">
-        <v>6523489</v>
+        <v>6523350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236916</v>
+        <v>113236893</v>
       </c>
       <c r="B42" t="n">
-        <v>95950</v>
+        <v>78713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,25 +4887,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4919,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306531</v>
+        <v>306585</v>
       </c>
       <c r="R42" t="n">
-        <v>6523473</v>
+        <v>6523469</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4981,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236926</v>
+        <v>113236910</v>
       </c>
       <c r="B43" t="n">
-        <v>91306</v>
+        <v>56781</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,25 +4989,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5021,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306544</v>
+        <v>306589</v>
       </c>
       <c r="R43" t="n">
-        <v>6523404</v>
+        <v>6523472</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5057,6 +5053,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5083,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236889</v>
+        <v>113236898</v>
       </c>
       <c r="B44" t="n">
-        <v>78713</v>
+        <v>56765</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5099,21 +5100,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5123,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306547</v>
+        <v>306506</v>
       </c>
       <c r="R44" t="n">
-        <v>6523388</v>
+        <v>6523348</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,6 +5160,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5185,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236912</v>
+        <v>113236900</v>
       </c>
       <c r="B45" t="n">
-        <v>91329</v>
+        <v>56765</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5201,21 +5207,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5225,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306536</v>
+        <v>306496</v>
       </c>
       <c r="R45" t="n">
-        <v>6523428</v>
+        <v>6523360</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5261,6 +5267,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5287,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236905</v>
+        <v>113236881</v>
       </c>
       <c r="B46" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5303,21 +5314,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5327,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306537</v>
+        <v>306645</v>
       </c>
       <c r="R46" t="n">
-        <v>6523319</v>
+        <v>6523507</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5363,11 +5374,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5394,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236898</v>
+        <v>113236887</v>
       </c>
       <c r="B47" t="n">
-        <v>56765</v>
+        <v>78713</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5410,21 +5416,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5434,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306506</v>
+        <v>306511</v>
       </c>
       <c r="R47" t="n">
-        <v>6523348</v>
+        <v>6523365</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5470,11 +5476,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5501,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236911</v>
+        <v>113236894</v>
       </c>
       <c r="B48" t="n">
-        <v>96277</v>
+        <v>78713</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,25 +5514,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306509</v>
+        <v>306589</v>
       </c>
       <c r="R48" t="n">
-        <v>6523483</v>
+        <v>6523489</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5585,7 +5586,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>113198467</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198462</v>
+        <v>113198463</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306631</v>
+        <v>306553</v>
       </c>
       <c r="R5" t="n">
-        <v>6523391</v>
+        <v>6523421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113198463</v>
+        <v>113198464</v>
       </c>
       <c r="B6" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306553</v>
+        <v>306551</v>
       </c>
       <c r="R6" t="n">
-        <v>6523421</v>
+        <v>6523451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,17 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113198464</v>
+        <v>113198462</v>
       </c>
       <c r="B7" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306551</v>
+        <v>306631</v>
       </c>
       <c r="R7" t="n">
-        <v>6523451</v>
+        <v>6523391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236968</v>
+        <v>113236899</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>56766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306575</v>
+        <v>306499</v>
       </c>
       <c r="R8" t="n">
-        <v>6523472</v>
+        <v>6523361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236969</v>
+        <v>113236913</v>
       </c>
       <c r="B9" t="n">
-        <v>91306</v>
+        <v>96292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306549</v>
+        <v>306509</v>
       </c>
       <c r="R9" t="n">
-        <v>6523459</v>
+        <v>6523355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,11 +1519,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236892</v>
+        <v>113236889</v>
       </c>
       <c r="B10" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306578</v>
+        <v>306547</v>
       </c>
       <c r="R10" t="n">
-        <v>6523473</v>
+        <v>6523388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236877</v>
+        <v>113236916</v>
       </c>
       <c r="B11" t="n">
-        <v>93755</v>
+        <v>95962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306513</v>
+        <v>306531</v>
       </c>
       <c r="R11" t="n">
-        <v>6523470</v>
+        <v>6523473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,7 +1752,7 @@
         <v>113236907</v>
       </c>
       <c r="B12" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236912</v>
+        <v>113236926</v>
       </c>
       <c r="B13" t="n">
-        <v>91329</v>
+        <v>91318</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306536</v>
+        <v>306544</v>
       </c>
       <c r="R13" t="n">
-        <v>6523428</v>
+        <v>6523404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236909</v>
+        <v>113236969</v>
       </c>
       <c r="B14" t="n">
-        <v>56781</v>
+        <v>91318</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,25 +1970,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306510</v>
+        <v>306549</v>
       </c>
       <c r="R14" t="n">
-        <v>6523383</v>
+        <v>6523459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,7 +2038,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2070,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236908</v>
+        <v>113236888</v>
       </c>
       <c r="B15" t="n">
-        <v>56781</v>
+        <v>78725</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,21 +2081,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306598</v>
+        <v>306512</v>
       </c>
       <c r="R15" t="n">
-        <v>6523398</v>
+        <v>6523350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2177,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236889</v>
+        <v>113236910</v>
       </c>
       <c r="B16" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,21 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306547</v>
+        <v>306589</v>
       </c>
       <c r="R16" t="n">
-        <v>6523388</v>
+        <v>6523472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,6 +2243,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236885</v>
+        <v>113236896</v>
       </c>
       <c r="B17" t="n">
-        <v>78713</v>
+        <v>56766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,21 +2290,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2319,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306496</v>
+        <v>306488</v>
       </c>
       <c r="R17" t="n">
-        <v>6523349</v>
+        <v>6523354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,6 +2350,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236895</v>
+        <v>113236903</v>
       </c>
       <c r="B18" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306645</v>
+        <v>306590</v>
       </c>
       <c r="R18" t="n">
-        <v>6523503</v>
+        <v>6523319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,6 +2457,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236905</v>
+        <v>113236885</v>
       </c>
       <c r="B19" t="n">
-        <v>56781</v>
+        <v>78725</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2504,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306537</v>
+        <v>306496</v>
       </c>
       <c r="R19" t="n">
-        <v>6523319</v>
+        <v>6523349</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,11 +2564,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236967</v>
+        <v>113236902</v>
       </c>
       <c r="B20" t="n">
-        <v>91306</v>
+        <v>56782</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,25 +2602,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306533</v>
+        <v>306520</v>
       </c>
       <c r="R20" t="n">
-        <v>6523475</v>
+        <v>6523332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236891</v>
+        <v>113236909</v>
       </c>
       <c r="B21" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,21 +2713,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306571</v>
+        <v>306510</v>
       </c>
       <c r="R21" t="n">
-        <v>6523493</v>
+        <v>6523383</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,6 +2773,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2799,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236916</v>
+        <v>113236891</v>
       </c>
       <c r="B22" t="n">
-        <v>95950</v>
+        <v>78725</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,25 +2816,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2839,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306531</v>
+        <v>306571</v>
       </c>
       <c r="R22" t="n">
-        <v>6523473</v>
+        <v>6523493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236890</v>
+        <v>113236883</v>
       </c>
       <c r="B23" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306572</v>
+        <v>306515</v>
       </c>
       <c r="R23" t="n">
-        <v>6523368</v>
+        <v>6523326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3008,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236883</v>
+        <v>113236904</v>
       </c>
       <c r="B24" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3024,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306515</v>
+        <v>306627</v>
       </c>
       <c r="R24" t="n">
-        <v>6523326</v>
+        <v>6523505</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,6 +3084,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3108,7 +3118,7 @@
         <v>113236897</v>
       </c>
       <c r="B25" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236926</v>
+        <v>113236900</v>
       </c>
       <c r="B26" t="n">
-        <v>91306</v>
+        <v>56766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3224,25 +3234,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3252,10 +3262,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306544</v>
+        <v>306496</v>
       </c>
       <c r="R26" t="n">
-        <v>6523404</v>
+        <v>6523360</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,6 +3298,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3314,10 +3329,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236906</v>
+        <v>113236967</v>
       </c>
       <c r="B27" t="n">
-        <v>56781</v>
+        <v>91318</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3326,25 +3341,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3354,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306644</v>
+        <v>306533</v>
       </c>
       <c r="R27" t="n">
-        <v>6523374</v>
+        <v>6523475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,7 +3409,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3421,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236925</v>
+        <v>113236884</v>
       </c>
       <c r="B28" t="n">
-        <v>91306</v>
+        <v>78725</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3461,10 +3476,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306594</v>
+        <v>306508</v>
       </c>
       <c r="R28" t="n">
-        <v>6523469</v>
+        <v>6523433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,10 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236882</v>
+        <v>113236898</v>
       </c>
       <c r="B29" t="n">
-        <v>78713</v>
+        <v>56766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3539,21 +3554,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3563,10 +3578,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306556</v>
+        <v>306506</v>
       </c>
       <c r="R29" t="n">
-        <v>6523344</v>
+        <v>6523348</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,6 +3614,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236902</v>
+        <v>113236912</v>
       </c>
       <c r="B30" t="n">
-        <v>56781</v>
+        <v>91341</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,21 +3661,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3665,10 +3685,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306520</v>
+        <v>306536</v>
       </c>
       <c r="R30" t="n">
-        <v>6523332</v>
+        <v>6523428</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3701,11 +3721,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3732,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236913</v>
+        <v>113236877</v>
       </c>
       <c r="B31" t="n">
-        <v>96280</v>
+        <v>93767</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,21 +3763,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221946</v>
+        <v>2810</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3772,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306509</v>
+        <v>306513</v>
       </c>
       <c r="R31" t="n">
-        <v>6523355</v>
+        <v>6523470</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3834,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236899</v>
+        <v>113236892</v>
       </c>
       <c r="B32" t="n">
-        <v>56765</v>
+        <v>78725</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,21 +3865,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3874,10 +3889,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306499</v>
+        <v>306578</v>
       </c>
       <c r="R32" t="n">
-        <v>6523361</v>
+        <v>6523473</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3910,11 +3925,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,10 +3951,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236896</v>
+        <v>113236886</v>
       </c>
       <c r="B33" t="n">
-        <v>56765</v>
+        <v>78725</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,21 +3967,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3981,10 +3991,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306488</v>
+        <v>306485</v>
       </c>
       <c r="R33" t="n">
-        <v>6523354</v>
+        <v>6523352</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,11 +4027,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,10 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236911</v>
+        <v>113236968</v>
       </c>
       <c r="B34" t="n">
-        <v>96277</v>
+        <v>91318</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,21 +4069,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4088,10 +4093,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306509</v>
+        <v>306575</v>
       </c>
       <c r="R34" t="n">
-        <v>6523483</v>
+        <v>6523472</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4126,13 +4131,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4151,10 +4160,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236886</v>
+        <v>113236905</v>
       </c>
       <c r="B35" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4167,21 +4176,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4191,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306485</v>
+        <v>306537</v>
       </c>
       <c r="R35" t="n">
-        <v>6523352</v>
+        <v>6523319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,6 +4236,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4253,10 +4267,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236884</v>
+        <v>113236895</v>
       </c>
       <c r="B36" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4293,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306508</v>
+        <v>306645</v>
       </c>
       <c r="R36" t="n">
-        <v>6523433</v>
+        <v>6523503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4355,10 +4369,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236876</v>
+        <v>113236894</v>
       </c>
       <c r="B37" t="n">
-        <v>93755</v>
+        <v>78725</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4367,25 +4381,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4395,10 +4409,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306543</v>
+        <v>306589</v>
       </c>
       <c r="R37" t="n">
-        <v>6523480</v>
+        <v>6523489</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4457,10 +4471,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236927</v>
+        <v>113236882</v>
       </c>
       <c r="B38" t="n">
-        <v>94108</v>
+        <v>78725</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4469,25 +4483,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4497,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306474</v>
+        <v>306556</v>
       </c>
       <c r="R38" t="n">
-        <v>6523353</v>
+        <v>6523344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4559,10 +4573,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236904</v>
+        <v>113236881</v>
       </c>
       <c r="B39" t="n">
-        <v>56781</v>
+        <v>78725</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4575,21 +4589,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4599,10 +4613,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306627</v>
+        <v>306645</v>
       </c>
       <c r="R39" t="n">
-        <v>6523505</v>
+        <v>6523507</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4635,11 +4649,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,10 +4675,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236903</v>
+        <v>113236893</v>
       </c>
       <c r="B40" t="n">
-        <v>56781</v>
+        <v>78725</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,21 +4691,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306590</v>
+        <v>306585</v>
       </c>
       <c r="R40" t="n">
-        <v>6523319</v>
+        <v>6523469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,11 +4751,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,10 +4777,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236888</v>
+        <v>113236911</v>
       </c>
       <c r="B41" t="n">
-        <v>78713</v>
+        <v>96289</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,25 +4789,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4817,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306512</v>
+        <v>306509</v>
       </c>
       <c r="R41" t="n">
-        <v>6523350</v>
+        <v>6523483</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4857,6 +4861,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4875,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236893</v>
+        <v>113236906</v>
       </c>
       <c r="B42" t="n">
-        <v>78713</v>
+        <v>56782</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,21 +4896,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4920,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306585</v>
+        <v>306644</v>
       </c>
       <c r="R42" t="n">
-        <v>6523469</v>
+        <v>6523374</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4951,6 +4956,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4977,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236910</v>
+        <v>113236908</v>
       </c>
       <c r="B43" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5017,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306589</v>
+        <v>306598</v>
       </c>
       <c r="R43" t="n">
-        <v>6523472</v>
+        <v>6523398</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,10 +5094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236898</v>
+        <v>113236925</v>
       </c>
       <c r="B44" t="n">
-        <v>56765</v>
+        <v>91318</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5096,25 +5106,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5124,10 +5134,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306506</v>
+        <v>306594</v>
       </c>
       <c r="R44" t="n">
-        <v>6523348</v>
+        <v>6523469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5160,11 +5170,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5191,10 +5196,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236900</v>
+        <v>113236890</v>
       </c>
       <c r="B45" t="n">
-        <v>56765</v>
+        <v>78725</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5207,21 +5212,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306496</v>
+        <v>306572</v>
       </c>
       <c r="R45" t="n">
-        <v>6523360</v>
+        <v>6523368</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5267,11 +5272,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236881</v>
+        <v>113236887</v>
       </c>
       <c r="B46" t="n">
-        <v>78713</v>
+        <v>78725</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5338,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306645</v>
+        <v>306511</v>
       </c>
       <c r="R46" t="n">
-        <v>6523507</v>
+        <v>6523365</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236887</v>
+        <v>113236927</v>
       </c>
       <c r="B47" t="n">
-        <v>78713</v>
+        <v>94120</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5412,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306511</v>
+        <v>306474</v>
       </c>
       <c r="R47" t="n">
-        <v>6523365</v>
+        <v>6523353</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236894</v>
+        <v>113236876</v>
       </c>
       <c r="B48" t="n">
-        <v>78713</v>
+        <v>93767</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,25 +5514,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306589</v>
+        <v>306543</v>
       </c>
       <c r="R48" t="n">
-        <v>6523489</v>
+        <v>6523480</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113198467</v>
+        <v>113198463</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,27 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306536</v>
+        <v>306553</v>
       </c>
       <c r="R4" t="n">
-        <v>6523466</v>
+        <v>6523421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,17 +988,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198463</v>
+        <v>113198462</v>
       </c>
       <c r="B5" t="n">
         <v>78725</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306553</v>
+        <v>306631</v>
       </c>
       <c r="R5" t="n">
-        <v>6523421</v>
+        <v>6523391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113198462</v>
+        <v>113198467</v>
       </c>
       <c r="B7" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,26 +1241,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1273,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306631</v>
+        <v>306536</v>
       </c>
       <c r="R7" t="n">
-        <v>6523391</v>
+        <v>6523466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,13 +1307,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236899</v>
+        <v>113236926</v>
       </c>
       <c r="B8" t="n">
-        <v>56766</v>
+        <v>91318</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306499</v>
+        <v>306544</v>
       </c>
       <c r="R8" t="n">
-        <v>6523361</v>
+        <v>6523404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236913</v>
+        <v>113236876</v>
       </c>
       <c r="B9" t="n">
-        <v>96292</v>
+        <v>93767</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306509</v>
+        <v>306543</v>
       </c>
       <c r="R9" t="n">
-        <v>6523355</v>
+        <v>6523480</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236889</v>
+        <v>113236894</v>
       </c>
       <c r="B10" t="n">
         <v>78725</v>
@@ -1585,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306547</v>
+        <v>306589</v>
       </c>
       <c r="R10" t="n">
-        <v>6523388</v>
+        <v>6523489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236916</v>
+        <v>113236888</v>
       </c>
       <c r="B11" t="n">
-        <v>95962</v>
+        <v>78725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1654,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306531</v>
+        <v>306512</v>
       </c>
       <c r="R11" t="n">
-        <v>6523473</v>
+        <v>6523350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236907</v>
+        <v>113236895</v>
       </c>
       <c r="B12" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,21 +1760,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306479</v>
+        <v>306645</v>
       </c>
       <c r="R12" t="n">
-        <v>6523383</v>
+        <v>6523503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,11 +1820,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236926</v>
+        <v>113236911</v>
       </c>
       <c r="B13" t="n">
-        <v>91318</v>
+        <v>96289</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306544</v>
+        <v>306509</v>
       </c>
       <c r="R13" t="n">
-        <v>6523404</v>
+        <v>6523483</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,6 +1930,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236969</v>
+        <v>113236908</v>
       </c>
       <c r="B14" t="n">
-        <v>91318</v>
+        <v>56782</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,25 +1961,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306549</v>
+        <v>306598</v>
       </c>
       <c r="R14" t="n">
-        <v>6523459</v>
+        <v>6523398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236888</v>
+        <v>113236890</v>
       </c>
       <c r="B15" t="n">
         <v>78725</v>
@@ -2105,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306512</v>
+        <v>306572</v>
       </c>
       <c r="R15" t="n">
-        <v>6523350</v>
+        <v>6523368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236910</v>
+        <v>113236905</v>
       </c>
       <c r="B16" t="n">
         <v>56782</v>
@@ -2207,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306589</v>
+        <v>306537</v>
       </c>
       <c r="R16" t="n">
-        <v>6523472</v>
+        <v>6523319</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236896</v>
+        <v>113236927</v>
       </c>
       <c r="B17" t="n">
-        <v>56766</v>
+        <v>94120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306488</v>
+        <v>306474</v>
       </c>
       <c r="R17" t="n">
-        <v>6523354</v>
+        <v>6523353</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236903</v>
+        <v>113236896</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,16 +2383,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2421,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306590</v>
+        <v>306488</v>
       </c>
       <c r="R18" t="n">
-        <v>6523319</v>
+        <v>6523354</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236885</v>
+        <v>113236897</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>56766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2528,7 +2514,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306496</v>
+        <v>306516</v>
       </c>
       <c r="R19" t="n">
         <v>6523349</v>
@@ -2564,6 +2550,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236902</v>
+        <v>113236906</v>
       </c>
       <c r="B20" t="n">
         <v>56782</v>
@@ -2630,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306520</v>
+        <v>306644</v>
       </c>
       <c r="R20" t="n">
-        <v>6523332</v>
+        <v>6523374</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236909</v>
+        <v>113236904</v>
       </c>
       <c r="B21" t="n">
         <v>56782</v>
@@ -2737,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306510</v>
+        <v>306627</v>
       </c>
       <c r="R21" t="n">
-        <v>6523383</v>
+        <v>6523505</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236891</v>
+        <v>113236893</v>
       </c>
       <c r="B22" t="n">
         <v>78725</v>
@@ -2844,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306571</v>
+        <v>306585</v>
       </c>
       <c r="R22" t="n">
-        <v>6523493</v>
+        <v>6523469</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2897,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236883</v>
+        <v>113236892</v>
       </c>
       <c r="B23" t="n">
         <v>78725</v>
@@ -2946,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306515</v>
+        <v>306578</v>
       </c>
       <c r="R23" t="n">
-        <v>6523326</v>
+        <v>6523473</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236904</v>
+        <v>113236887</v>
       </c>
       <c r="B24" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3048,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306627</v>
+        <v>306511</v>
       </c>
       <c r="R24" t="n">
-        <v>6523505</v>
+        <v>6523365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3084,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3115,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236897</v>
+        <v>113236884</v>
       </c>
       <c r="B25" t="n">
-        <v>56766</v>
+        <v>78725</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3155,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306516</v>
+        <v>306508</v>
       </c>
       <c r="R25" t="n">
-        <v>6523349</v>
+        <v>6523433</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,11 +3177,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,7 +3203,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236900</v>
+        <v>113236899</v>
       </c>
       <c r="B26" t="n">
         <v>56766</v>
@@ -3262,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306496</v>
+        <v>306499</v>
       </c>
       <c r="R26" t="n">
-        <v>6523360</v>
+        <v>6523361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3329,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236967</v>
+        <v>113236913</v>
       </c>
       <c r="B27" t="n">
-        <v>91318</v>
+        <v>96292</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3345,21 +3326,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3369,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306533</v>
+        <v>306509</v>
       </c>
       <c r="R27" t="n">
-        <v>6523475</v>
+        <v>6523355</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,11 +3386,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3436,7 +3412,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236884</v>
+        <v>113236885</v>
       </c>
       <c r="B28" t="n">
         <v>78725</v>
@@ -3476,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306508</v>
+        <v>306496</v>
       </c>
       <c r="R28" t="n">
-        <v>6523433</v>
+        <v>6523349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236898</v>
+        <v>113236968</v>
       </c>
       <c r="B29" t="n">
-        <v>56766</v>
+        <v>91318</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3550,25 +3526,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3578,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306506</v>
+        <v>306575</v>
       </c>
       <c r="R29" t="n">
-        <v>6523348</v>
+        <v>6523472</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3594,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3645,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236912</v>
+        <v>113236925</v>
       </c>
       <c r="B30" t="n">
-        <v>91341</v>
+        <v>91318</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3685,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306536</v>
+        <v>306594</v>
       </c>
       <c r="R30" t="n">
-        <v>6523428</v>
+        <v>6523469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236877</v>
+        <v>113236969</v>
       </c>
       <c r="B31" t="n">
-        <v>93767</v>
+        <v>91318</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,21 +3739,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3787,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306513</v>
+        <v>306549</v>
       </c>
       <c r="R31" t="n">
-        <v>6523470</v>
+        <v>6523459</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,6 +3799,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236892</v>
+        <v>113236909</v>
       </c>
       <c r="B32" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,21 +3846,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3889,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306578</v>
+        <v>306510</v>
       </c>
       <c r="R32" t="n">
-        <v>6523473</v>
+        <v>6523383</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3925,6 +3906,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236886</v>
+        <v>113236903</v>
       </c>
       <c r="B33" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,21 +3953,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3991,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306485</v>
+        <v>306590</v>
       </c>
       <c r="R33" t="n">
-        <v>6523352</v>
+        <v>6523319</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4027,6 +4013,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4053,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236968</v>
+        <v>113236912</v>
       </c>
       <c r="B34" t="n">
-        <v>91318</v>
+        <v>91341</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4065,25 +4056,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4093,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306575</v>
+        <v>306536</v>
       </c>
       <c r="R34" t="n">
-        <v>6523472</v>
+        <v>6523428</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4129,11 +4120,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4160,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236905</v>
+        <v>113236891</v>
       </c>
       <c r="B35" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4176,21 +4162,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306537</v>
+        <v>306571</v>
       </c>
       <c r="R35" t="n">
-        <v>6523319</v>
+        <v>6523493</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4236,11 +4222,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4267,7 +4248,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236895</v>
+        <v>113236886</v>
       </c>
       <c r="B36" t="n">
         <v>78725</v>
@@ -4307,10 +4288,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306645</v>
+        <v>306485</v>
       </c>
       <c r="R36" t="n">
-        <v>6523503</v>
+        <v>6523352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4369,7 +4350,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236894</v>
+        <v>113236882</v>
       </c>
       <c r="B37" t="n">
         <v>78725</v>
@@ -4409,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306589</v>
+        <v>306556</v>
       </c>
       <c r="R37" t="n">
-        <v>6523489</v>
+        <v>6523344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236882</v>
+        <v>113236877</v>
       </c>
       <c r="B38" t="n">
-        <v>78725</v>
+        <v>93767</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,25 +4464,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4492,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306556</v>
+        <v>306513</v>
       </c>
       <c r="R38" t="n">
-        <v>6523344</v>
+        <v>6523470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4573,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236881</v>
+        <v>113236907</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4589,21 +4570,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4613,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306645</v>
+        <v>306479</v>
       </c>
       <c r="R39" t="n">
-        <v>6523507</v>
+        <v>6523383</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4649,6 +4630,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4675,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236893</v>
+        <v>113236900</v>
       </c>
       <c r="B40" t="n">
-        <v>78725</v>
+        <v>56766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4691,21 +4677,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4715,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306585</v>
+        <v>306496</v>
       </c>
       <c r="R40" t="n">
-        <v>6523469</v>
+        <v>6523360</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,6 +4737,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4777,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236911</v>
+        <v>113236883</v>
       </c>
       <c r="B41" t="n">
-        <v>96289</v>
+        <v>78725</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4789,25 +4780,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4817,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306509</v>
+        <v>306515</v>
       </c>
       <c r="R41" t="n">
-        <v>6523483</v>
+        <v>6523326</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4861,7 +4852,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236906</v>
+        <v>113236916</v>
       </c>
       <c r="B42" t="n">
-        <v>56782</v>
+        <v>95962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4892,25 +4882,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4920,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306644</v>
+        <v>306531</v>
       </c>
       <c r="R42" t="n">
-        <v>6523374</v>
+        <v>6523473</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4956,11 +4946,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,7 +4972,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236908</v>
+        <v>113236902</v>
       </c>
       <c r="B43" t="n">
         <v>56782</v>
@@ -5027,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306598</v>
+        <v>306520</v>
       </c>
       <c r="R43" t="n">
-        <v>6523398</v>
+        <v>6523332</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,7 +5052,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236925</v>
+        <v>113236898</v>
       </c>
       <c r="B44" t="n">
-        <v>91318</v>
+        <v>56766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5106,25 +5091,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5134,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306594</v>
+        <v>306506</v>
       </c>
       <c r="R44" t="n">
-        <v>6523469</v>
+        <v>6523348</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5170,6 +5155,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5196,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236890</v>
+        <v>113236967</v>
       </c>
       <c r="B45" t="n">
-        <v>78725</v>
+        <v>91318</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5208,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306572</v>
+        <v>306533</v>
       </c>
       <c r="R45" t="n">
-        <v>6523368</v>
+        <v>6523475</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5272,6 +5262,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5298,7 +5293,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236887</v>
+        <v>113236881</v>
       </c>
       <c r="B46" t="n">
         <v>78725</v>
@@ -5338,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306511</v>
+        <v>306645</v>
       </c>
       <c r="R46" t="n">
-        <v>6523365</v>
+        <v>6523507</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236927</v>
+        <v>113236889</v>
       </c>
       <c r="B47" t="n">
-        <v>94120</v>
+        <v>78725</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306474</v>
+        <v>306547</v>
       </c>
       <c r="R47" t="n">
-        <v>6523353</v>
+        <v>6523388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236876</v>
+        <v>113236910</v>
       </c>
       <c r="B48" t="n">
-        <v>93767</v>
+        <v>56782</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306543</v>
+        <v>306589</v>
       </c>
       <c r="R48" t="n">
-        <v>6523480</v>
+        <v>6523472</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5578,6 +5573,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236890</v>
+        <v>113236905</v>
       </c>
       <c r="B15" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306572</v>
+        <v>306537</v>
       </c>
       <c r="R15" t="n">
-        <v>6523368</v>
+        <v>6523319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236905</v>
+        <v>113236890</v>
       </c>
       <c r="B16" t="n">
-        <v>56782</v>
+        <v>78725</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306537</v>
+        <v>306572</v>
       </c>
       <c r="R16" t="n">
-        <v>6523319</v>
+        <v>6523368</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4044,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236912</v>
+        <v>113236877</v>
       </c>
       <c r="B34" t="n">
-        <v>91341</v>
+        <v>93767</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4056,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>2810</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306536</v>
+        <v>306513</v>
       </c>
       <c r="R34" t="n">
-        <v>6523428</v>
+        <v>6523470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236891</v>
+        <v>113236912</v>
       </c>
       <c r="B35" t="n">
-        <v>78725</v>
+        <v>91341</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4162,21 +4162,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306571</v>
+        <v>306536</v>
       </c>
       <c r="R35" t="n">
-        <v>6523493</v>
+        <v>6523428</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236886</v>
+        <v>113236891</v>
       </c>
       <c r="B36" t="n">
         <v>78725</v>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306485</v>
+        <v>306571</v>
       </c>
       <c r="R36" t="n">
-        <v>6523352</v>
+        <v>6523493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236882</v>
+        <v>113236886</v>
       </c>
       <c r="B37" t="n">
         <v>78725</v>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306556</v>
+        <v>306485</v>
       </c>
       <c r="R37" t="n">
-        <v>6523344</v>
+        <v>6523352</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236877</v>
+        <v>113236882</v>
       </c>
       <c r="B38" t="n">
-        <v>93767</v>
+        <v>78725</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4464,25 +4464,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4492,10 +4492,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306513</v>
+        <v>306556</v>
       </c>
       <c r="R38" t="n">
-        <v>6523470</v>
+        <v>6523344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236900</v>
+        <v>113236902</v>
       </c>
       <c r="B40" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4677,16 +4677,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306496</v>
+        <v>306520</v>
       </c>
       <c r="R40" t="n">
-        <v>6523360</v>
+        <v>6523332</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236902</v>
+        <v>113236900</v>
       </c>
       <c r="B43" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306520</v>
+        <v>306496</v>
       </c>
       <c r="R43" t="n">
-        <v>6523332</v>
+        <v>6523360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236898</v>
+        <v>113236967</v>
       </c>
       <c r="B44" t="n">
-        <v>56766</v>
+        <v>91318</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5091,25 +5091,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306506</v>
+        <v>306533</v>
       </c>
       <c r="R44" t="n">
-        <v>6523348</v>
+        <v>6523475</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236967</v>
+        <v>113236881</v>
       </c>
       <c r="B45" t="n">
-        <v>91318</v>
+        <v>78725</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306533</v>
+        <v>306645</v>
       </c>
       <c r="R45" t="n">
-        <v>6523475</v>
+        <v>6523507</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,11 +5262,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,7 +5288,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236881</v>
+        <v>113236889</v>
       </c>
       <c r="B46" t="n">
         <v>78725</v>
@@ -5333,10 +5328,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306645</v>
+        <v>306547</v>
       </c>
       <c r="R46" t="n">
-        <v>6523507</v>
+        <v>6523388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236889</v>
+        <v>113236910</v>
       </c>
       <c r="B47" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5406,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306547</v>
+        <v>306589</v>
       </c>
       <c r="R47" t="n">
-        <v>6523388</v>
+        <v>6523472</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,6 +5466,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236910</v>
+        <v>113236898</v>
       </c>
       <c r="B48" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,16 +5513,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306589</v>
+        <v>306506</v>
       </c>
       <c r="R48" t="n">
-        <v>6523472</v>
+        <v>6523348</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113198463</v>
+        <v>113198467</v>
       </c>
       <c r="B4" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,26 +923,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306553</v>
+        <v>306536</v>
       </c>
       <c r="R4" t="n">
-        <v>6523421</v>
+        <v>6523466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,13 +989,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198462</v>
+        <v>113198463</v>
       </c>
       <c r="B5" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306631</v>
+        <v>306553</v>
       </c>
       <c r="R5" t="n">
-        <v>6523391</v>
+        <v>6523421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1117,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1122,7 +1127,7 @@
         <v>113198464</v>
       </c>
       <c r="B6" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1225,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113198467</v>
+        <v>113198462</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>78747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,27 +1246,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306536</v>
+        <v>306631</v>
       </c>
       <c r="R7" t="n">
-        <v>6523466</v>
+        <v>6523391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,17 +1311,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236926</v>
+        <v>113236911</v>
       </c>
       <c r="B8" t="n">
-        <v>91318</v>
+        <v>96311</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306544</v>
+        <v>306509</v>
       </c>
       <c r="R8" t="n">
-        <v>6523404</v>
+        <v>6523483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,6 +1420,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236876</v>
+        <v>113236896</v>
       </c>
       <c r="B9" t="n">
-        <v>93767</v>
+        <v>56766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,25 +1451,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306543</v>
+        <v>306488</v>
       </c>
       <c r="R9" t="n">
-        <v>6523480</v>
+        <v>6523354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236894</v>
+        <v>113236891</v>
       </c>
       <c r="B10" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306589</v>
+        <v>306571</v>
       </c>
       <c r="R10" t="n">
-        <v>6523489</v>
+        <v>6523493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236888</v>
+        <v>113236908</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306512</v>
+        <v>306598</v>
       </c>
       <c r="R11" t="n">
-        <v>6523350</v>
+        <v>6523398</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236895</v>
+        <v>113236877</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>93789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1784,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306645</v>
+        <v>306513</v>
       </c>
       <c r="R12" t="n">
-        <v>6523503</v>
+        <v>6523470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236911</v>
+        <v>113236898</v>
       </c>
       <c r="B13" t="n">
-        <v>96289</v>
+        <v>56766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1869,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306509</v>
+        <v>306506</v>
       </c>
       <c r="R13" t="n">
-        <v>6523483</v>
+        <v>6523348</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,13 +1935,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1949,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236908</v>
+        <v>113236899</v>
       </c>
       <c r="B14" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,16 +1980,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1989,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306598</v>
+        <v>306499</v>
       </c>
       <c r="R14" t="n">
-        <v>6523398</v>
+        <v>6523361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2044,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236905</v>
+        <v>113236913</v>
       </c>
       <c r="B15" t="n">
-        <v>56782</v>
+        <v>96314</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306537</v>
+        <v>306509</v>
       </c>
       <c r="R15" t="n">
-        <v>6523319</v>
+        <v>6523355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2147,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236890</v>
+        <v>113236895</v>
       </c>
       <c r="B16" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306572</v>
+        <v>306645</v>
       </c>
       <c r="R16" t="n">
-        <v>6523368</v>
+        <v>6523503</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236927</v>
+        <v>113236892</v>
       </c>
       <c r="B17" t="n">
-        <v>94120</v>
+        <v>78747</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306474</v>
+        <v>306578</v>
       </c>
       <c r="R17" t="n">
-        <v>6523353</v>
+        <v>6523473</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236896</v>
+        <v>113236904</v>
       </c>
       <c r="B18" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,16 +2393,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2407,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306488</v>
+        <v>306627</v>
       </c>
       <c r="R18" t="n">
-        <v>6523354</v>
+        <v>6523505</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236897</v>
+        <v>113236888</v>
       </c>
       <c r="B19" t="n">
-        <v>56766</v>
+        <v>78747</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2500,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306516</v>
+        <v>306512</v>
       </c>
       <c r="R19" t="n">
-        <v>6523349</v>
+        <v>6523350</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236906</v>
+        <v>113236893</v>
       </c>
       <c r="B20" t="n">
-        <v>56782</v>
+        <v>78747</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306644</v>
+        <v>306585</v>
       </c>
       <c r="R20" t="n">
-        <v>6523374</v>
+        <v>6523469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2662,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236904</v>
+        <v>113236885</v>
       </c>
       <c r="B21" t="n">
-        <v>56782</v>
+        <v>78747</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306627</v>
+        <v>306496</v>
       </c>
       <c r="R21" t="n">
-        <v>6523505</v>
+        <v>6523349</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,11 +2764,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236893</v>
+        <v>113236889</v>
       </c>
       <c r="B22" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306585</v>
+        <v>306547</v>
       </c>
       <c r="R22" t="n">
-        <v>6523469</v>
+        <v>6523388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236892</v>
+        <v>113236906</v>
       </c>
       <c r="B23" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306578</v>
+        <v>306644</v>
       </c>
       <c r="R23" t="n">
-        <v>6523473</v>
+        <v>6523374</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236887</v>
+        <v>113236890</v>
       </c>
       <c r="B24" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306511</v>
+        <v>306572</v>
       </c>
       <c r="R24" t="n">
-        <v>6523365</v>
+        <v>6523368</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236884</v>
+        <v>113236912</v>
       </c>
       <c r="B25" t="n">
-        <v>78725</v>
+        <v>91363</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306508</v>
+        <v>306536</v>
       </c>
       <c r="R25" t="n">
-        <v>6523433</v>
+        <v>6523428</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236899</v>
+        <v>113236925</v>
       </c>
       <c r="B26" t="n">
-        <v>56766</v>
+        <v>91340</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,25 +3215,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306499</v>
+        <v>306594</v>
       </c>
       <c r="R26" t="n">
-        <v>6523361</v>
+        <v>6523469</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,11 +3279,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,10 +3305,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236913</v>
+        <v>113236910</v>
       </c>
       <c r="B27" t="n">
-        <v>96292</v>
+        <v>56782</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3317,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306509</v>
+        <v>306589</v>
       </c>
       <c r="R27" t="n">
-        <v>6523355</v>
+        <v>6523472</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,6 +3381,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236885</v>
+        <v>113236887</v>
       </c>
       <c r="B28" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306496</v>
+        <v>306511</v>
       </c>
       <c r="R28" t="n">
-        <v>6523349</v>
+        <v>6523365</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236968</v>
+        <v>113236969</v>
       </c>
       <c r="B29" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306575</v>
+        <v>306549</v>
       </c>
       <c r="R29" t="n">
-        <v>6523472</v>
+        <v>6523459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236925</v>
+        <v>113236894</v>
       </c>
       <c r="B30" t="n">
-        <v>91318</v>
+        <v>78747</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,25 +3633,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306594</v>
+        <v>306589</v>
       </c>
       <c r="R30" t="n">
-        <v>6523469</v>
+        <v>6523489</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236969</v>
+        <v>113236926</v>
       </c>
       <c r="B31" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306549</v>
+        <v>306544</v>
       </c>
       <c r="R31" t="n">
-        <v>6523459</v>
+        <v>6523404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,11 +3799,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236909</v>
+        <v>113236884</v>
       </c>
       <c r="B32" t="n">
-        <v>56782</v>
+        <v>78747</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,21 +3841,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3870,10 +3865,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306510</v>
+        <v>306508</v>
       </c>
       <c r="R32" t="n">
-        <v>6523383</v>
+        <v>6523433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,11 +3901,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,10 +3927,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236903</v>
+        <v>113236967</v>
       </c>
       <c r="B33" t="n">
-        <v>56782</v>
+        <v>91340</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3949,25 +3939,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3977,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306590</v>
+        <v>306533</v>
       </c>
       <c r="R33" t="n">
-        <v>6523319</v>
+        <v>6523475</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,7 +4007,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4044,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236877</v>
+        <v>113236882</v>
       </c>
       <c r="B34" t="n">
-        <v>93767</v>
+        <v>78747</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4046,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4074,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306513</v>
+        <v>306556</v>
       </c>
       <c r="R34" t="n">
-        <v>6523470</v>
+        <v>6523344</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,10 +4136,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236912</v>
+        <v>113236916</v>
       </c>
       <c r="B35" t="n">
-        <v>91341</v>
+        <v>95984</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4158,25 +4148,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4186,10 +4176,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306536</v>
+        <v>306531</v>
       </c>
       <c r="R35" t="n">
-        <v>6523428</v>
+        <v>6523473</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4248,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236891</v>
+        <v>113236900</v>
       </c>
       <c r="B36" t="n">
-        <v>78725</v>
+        <v>56766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,21 +4254,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4288,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306571</v>
+        <v>306496</v>
       </c>
       <c r="R36" t="n">
-        <v>6523493</v>
+        <v>6523360</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,6 +4314,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,10 +4345,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236886</v>
+        <v>113236927</v>
       </c>
       <c r="B37" t="n">
-        <v>78725</v>
+        <v>94142</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4362,25 +4357,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4385,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306485</v>
+        <v>306474</v>
       </c>
       <c r="R37" t="n">
-        <v>6523352</v>
+        <v>6523353</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,10 +4447,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236882</v>
+        <v>113236905</v>
       </c>
       <c r="B38" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4468,21 +4463,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4492,10 +4487,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306556</v>
+        <v>306537</v>
       </c>
       <c r="R38" t="n">
-        <v>6523344</v>
+        <v>6523319</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4528,6 +4523,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,7 +4554,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236907</v>
+        <v>113236903</v>
       </c>
       <c r="B39" t="n">
         <v>56782</v>
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306479</v>
+        <v>306590</v>
       </c>
       <c r="R39" t="n">
-        <v>6523383</v>
+        <v>6523319</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236883</v>
+        <v>113236886</v>
       </c>
       <c r="B41" t="n">
-        <v>78725</v>
+        <v>78747</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306515</v>
+        <v>306485</v>
       </c>
       <c r="R41" t="n">
-        <v>6523326</v>
+        <v>6523352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236916</v>
+        <v>113236883</v>
       </c>
       <c r="B42" t="n">
-        <v>95962</v>
+        <v>78747</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4882,25 +4882,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306531</v>
+        <v>306515</v>
       </c>
       <c r="R42" t="n">
-        <v>6523473</v>
+        <v>6523326</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236900</v>
+        <v>113236909</v>
       </c>
       <c r="B43" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306496</v>
+        <v>306510</v>
       </c>
       <c r="R43" t="n">
-        <v>6523360</v>
+        <v>6523383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5079,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236967</v>
+        <v>113236968</v>
       </c>
       <c r="B44" t="n">
-        <v>91318</v>
+        <v>91340</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306533</v>
+        <v>306575</v>
       </c>
       <c r="R44" t="n">
-        <v>6523475</v>
+        <v>6523472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236881</v>
+        <v>113236907</v>
       </c>
       <c r="B45" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306645</v>
+        <v>306479</v>
       </c>
       <c r="R45" t="n">
-        <v>6523507</v>
+        <v>6523383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5262,6 +5262,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5288,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236889</v>
+        <v>113236897</v>
       </c>
       <c r="B46" t="n">
-        <v>78725</v>
+        <v>56766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,21 +5309,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5328,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306547</v>
+        <v>306516</v>
       </c>
       <c r="R46" t="n">
-        <v>6523388</v>
+        <v>6523349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5364,6 +5369,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236910</v>
+        <v>113236881</v>
       </c>
       <c r="B47" t="n">
-        <v>56782</v>
+        <v>78747</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5406,21 +5416,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5430,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306589</v>
+        <v>306645</v>
       </c>
       <c r="R47" t="n">
-        <v>6523472</v>
+        <v>6523507</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5466,11 +5476,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236898</v>
+        <v>113236876</v>
       </c>
       <c r="B48" t="n">
-        <v>56766</v>
+        <v>93789</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5514,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2810</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306506</v>
+        <v>306543</v>
       </c>
       <c r="R48" t="n">
-        <v>6523348</v>
+        <v>6523480</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5573,11 +5578,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113198467</v>
+        <v>113198462</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,27 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306536</v>
+        <v>306631</v>
       </c>
       <c r="R4" t="n">
-        <v>6523466</v>
+        <v>6523391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,17 +988,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,17 +1006,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
+          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113198463</v>
+        <v>113198467</v>
       </c>
       <c r="B5" t="n">
-        <v>78747</v>
+        <v>56785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,26 +1029,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306553</v>
+        <v>306536</v>
       </c>
       <c r="R5" t="n">
-        <v>6523421</v>
+        <v>6523466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,13 +1095,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113198464</v>
+        <v>113198463</v>
       </c>
       <c r="B6" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306551</v>
+        <v>306553</v>
       </c>
       <c r="R6" t="n">
-        <v>6523451</v>
+        <v>6523421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,17 +1223,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonathan Lindberg, Amanda Tas, gunilla hamne</t>
+          <t>Jonathan Lindberg, gunilla hamne, Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113198462</v>
+        <v>113198464</v>
       </c>
       <c r="B7" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306631</v>
+        <v>306551</v>
       </c>
       <c r="R7" t="n">
-        <v>6523391</v>
+        <v>6523451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236911</v>
+        <v>113236927</v>
       </c>
       <c r="B8" t="n">
-        <v>96311</v>
+        <v>94146</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306509</v>
+        <v>306474</v>
       </c>
       <c r="R8" t="n">
-        <v>6523483</v>
+        <v>6523353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236896</v>
+        <v>113236903</v>
       </c>
       <c r="B9" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,16 +1454,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1479,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306488</v>
+        <v>306590</v>
       </c>
       <c r="R9" t="n">
-        <v>6523354</v>
+        <v>6523319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236891</v>
+        <v>113236904</v>
       </c>
       <c r="B10" t="n">
-        <v>78747</v>
+        <v>56785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306571</v>
+        <v>306627</v>
       </c>
       <c r="R10" t="n">
-        <v>6523493</v>
+        <v>6523505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,6 +1621,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,7 +1655,7 @@
         <v>113236908</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236877</v>
+        <v>113236911</v>
       </c>
       <c r="B12" t="n">
-        <v>93789</v>
+        <v>96315</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306513</v>
+        <v>306509</v>
       </c>
       <c r="R12" t="n">
-        <v>6523470</v>
+        <v>6523483</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,6 +1843,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236898</v>
+        <v>113236881</v>
       </c>
       <c r="B13" t="n">
-        <v>56766</v>
+        <v>78751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306506</v>
+        <v>306645</v>
       </c>
       <c r="R13" t="n">
-        <v>6523348</v>
+        <v>6523507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,11 +1938,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236899</v>
+        <v>113236909</v>
       </c>
       <c r="B14" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,16 +1980,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306499</v>
+        <v>306510</v>
       </c>
       <c r="R14" t="n">
-        <v>6523361</v>
+        <v>6523383</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236913</v>
+        <v>113236968</v>
       </c>
       <c r="B15" t="n">
-        <v>96314</v>
+        <v>91344</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306509</v>
+        <v>306575</v>
       </c>
       <c r="R15" t="n">
-        <v>6523355</v>
+        <v>6523472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,6 +2147,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236895</v>
+        <v>113236882</v>
       </c>
       <c r="B16" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306645</v>
+        <v>306556</v>
       </c>
       <c r="R16" t="n">
-        <v>6523503</v>
+        <v>6523344</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2278,7 +2283,7 @@
         <v>113236892</v>
       </c>
       <c r="B17" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236904</v>
+        <v>113236884</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306627</v>
+        <v>306508</v>
       </c>
       <c r="R18" t="n">
-        <v>6523505</v>
+        <v>6523433</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236888</v>
+        <v>113236877</v>
       </c>
       <c r="B19" t="n">
-        <v>78747</v>
+        <v>93793</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,25 +2496,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306512</v>
+        <v>306513</v>
       </c>
       <c r="R19" t="n">
-        <v>6523350</v>
+        <v>6523470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236893</v>
+        <v>113236898</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>56769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306585</v>
+        <v>306506</v>
       </c>
       <c r="R20" t="n">
-        <v>6523469</v>
+        <v>6523348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,6 +2662,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236885</v>
+        <v>113236889</v>
       </c>
       <c r="B21" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306496</v>
+        <v>306547</v>
       </c>
       <c r="R21" t="n">
-        <v>6523349</v>
+        <v>6523388</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236889</v>
+        <v>113236887</v>
       </c>
       <c r="B22" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306547</v>
+        <v>306511</v>
       </c>
       <c r="R22" t="n">
-        <v>6523388</v>
+        <v>6523365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236906</v>
+        <v>113236883</v>
       </c>
       <c r="B23" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306644</v>
+        <v>306515</v>
       </c>
       <c r="R23" t="n">
-        <v>6523374</v>
+        <v>6523326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,11 +2973,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236890</v>
+        <v>113236969</v>
       </c>
       <c r="B24" t="n">
-        <v>78747</v>
+        <v>91344</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,25 +3011,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306572</v>
+        <v>306549</v>
       </c>
       <c r="R24" t="n">
-        <v>6523368</v>
+        <v>6523459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3075,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3101,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236912</v>
+        <v>113236926</v>
       </c>
       <c r="B25" t="n">
-        <v>91363</v>
+        <v>91344</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,25 +3118,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3146,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306536</v>
+        <v>306544</v>
       </c>
       <c r="R25" t="n">
-        <v>6523428</v>
+        <v>6523404</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3203,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236925</v>
+        <v>113236888</v>
       </c>
       <c r="B26" t="n">
-        <v>91340</v>
+        <v>78751</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3215,25 +3220,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3243,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306594</v>
+        <v>306512</v>
       </c>
       <c r="R26" t="n">
-        <v>6523469</v>
+        <v>6523350</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236910</v>
+        <v>113236896</v>
       </c>
       <c r="B27" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,16 +3326,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306589</v>
+        <v>306488</v>
       </c>
       <c r="R27" t="n">
-        <v>6523472</v>
+        <v>6523354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,7 +3390,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236887</v>
+        <v>113236893</v>
       </c>
       <c r="B28" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306511</v>
+        <v>306585</v>
       </c>
       <c r="R28" t="n">
-        <v>6523365</v>
+        <v>6523469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236969</v>
+        <v>113236907</v>
       </c>
       <c r="B29" t="n">
-        <v>91340</v>
+        <v>56785</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,25 +3531,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306549</v>
+        <v>306479</v>
       </c>
       <c r="R29" t="n">
-        <v>6523459</v>
+        <v>6523383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3599,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236894</v>
+        <v>113236902</v>
       </c>
       <c r="B30" t="n">
-        <v>78747</v>
+        <v>56785</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3642,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306589</v>
+        <v>306520</v>
       </c>
       <c r="R30" t="n">
-        <v>6523489</v>
+        <v>6523332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,6 +3702,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3733,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236926</v>
+        <v>113236897</v>
       </c>
       <c r="B31" t="n">
-        <v>91340</v>
+        <v>56769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3735,25 +3745,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3763,10 +3773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306544</v>
+        <v>306516</v>
       </c>
       <c r="R31" t="n">
-        <v>6523404</v>
+        <v>6523349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,6 +3809,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3825,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236884</v>
+        <v>113236913</v>
       </c>
       <c r="B32" t="n">
-        <v>78747</v>
+        <v>96318</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3837,25 +3852,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3865,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306508</v>
+        <v>306509</v>
       </c>
       <c r="R32" t="n">
-        <v>6523433</v>
+        <v>6523355</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3927,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236967</v>
+        <v>113236890</v>
       </c>
       <c r="B33" t="n">
-        <v>91340</v>
+        <v>78751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3939,25 +3954,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306533</v>
+        <v>306572</v>
       </c>
       <c r="R33" t="n">
-        <v>6523475</v>
+        <v>6523368</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,11 +4018,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4034,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236882</v>
+        <v>113236925</v>
       </c>
       <c r="B34" t="n">
-        <v>78747</v>
+        <v>91344</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,25 +4056,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4074,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306556</v>
+        <v>306594</v>
       </c>
       <c r="R34" t="n">
-        <v>6523344</v>
+        <v>6523469</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4136,10 +4146,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236916</v>
+        <v>113236905</v>
       </c>
       <c r="B35" t="n">
-        <v>95984</v>
+        <v>56785</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4148,25 +4158,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4176,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306531</v>
+        <v>306537</v>
       </c>
       <c r="R35" t="n">
-        <v>6523473</v>
+        <v>6523319</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4212,6 +4222,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4241,7 +4256,7 @@
         <v>113236900</v>
       </c>
       <c r="B36" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4345,10 +4360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236927</v>
+        <v>113236885</v>
       </c>
       <c r="B37" t="n">
-        <v>94142</v>
+        <v>78751</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,25 +4372,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4385,10 +4400,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306474</v>
+        <v>306496</v>
       </c>
       <c r="R37" t="n">
-        <v>6523353</v>
+        <v>6523349</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4447,10 +4462,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236905</v>
+        <v>113236894</v>
       </c>
       <c r="B38" t="n">
-        <v>56782</v>
+        <v>78751</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4463,21 +4478,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4487,10 +4502,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306537</v>
+        <v>306589</v>
       </c>
       <c r="R38" t="n">
-        <v>6523319</v>
+        <v>6523489</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4523,11 +4538,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236903</v>
+        <v>113236912</v>
       </c>
       <c r="B39" t="n">
-        <v>56782</v>
+        <v>91367</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4570,21 +4580,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4594,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306590</v>
+        <v>306536</v>
       </c>
       <c r="R39" t="n">
-        <v>6523319</v>
+        <v>6523428</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4630,11 +4640,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4661,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236902</v>
+        <v>113236916</v>
       </c>
       <c r="B40" t="n">
-        <v>56782</v>
+        <v>95988</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4673,25 +4678,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4701,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306520</v>
+        <v>306531</v>
       </c>
       <c r="R40" t="n">
-        <v>6523332</v>
+        <v>6523473</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4737,11 +4742,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4768,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236886</v>
+        <v>113236891</v>
       </c>
       <c r="B41" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306485</v>
+        <v>306571</v>
       </c>
       <c r="R41" t="n">
-        <v>6523352</v>
+        <v>6523493</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236883</v>
+        <v>113236886</v>
       </c>
       <c r="B42" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306515</v>
+        <v>306485</v>
       </c>
       <c r="R42" t="n">
-        <v>6523326</v>
+        <v>6523352</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236909</v>
+        <v>113236876</v>
       </c>
       <c r="B43" t="n">
-        <v>56782</v>
+        <v>93793</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,25 +4984,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306510</v>
+        <v>306543</v>
       </c>
       <c r="R43" t="n">
-        <v>6523383</v>
+        <v>6523480</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5048,11 +5048,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5079,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236968</v>
+        <v>113236906</v>
       </c>
       <c r="B44" t="n">
-        <v>91340</v>
+        <v>56785</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5091,25 +5086,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5114,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306575</v>
+        <v>306644</v>
       </c>
       <c r="R44" t="n">
-        <v>6523472</v>
+        <v>6523374</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,7 +5154,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236907</v>
+        <v>113236910</v>
       </c>
       <c r="B45" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5226,10 +5221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306479</v>
+        <v>306589</v>
       </c>
       <c r="R45" t="n">
-        <v>6523383</v>
+        <v>6523472</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236897</v>
+        <v>113236895</v>
       </c>
       <c r="B46" t="n">
-        <v>56766</v>
+        <v>78751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5309,21 +5304,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5328,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306516</v>
+        <v>306645</v>
       </c>
       <c r="R46" t="n">
-        <v>6523349</v>
+        <v>6523503</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5369,11 +5364,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236881</v>
+        <v>113236899</v>
       </c>
       <c r="B47" t="n">
-        <v>78747</v>
+        <v>56769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5416,21 +5406,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306645</v>
+        <v>306499</v>
       </c>
       <c r="R47" t="n">
-        <v>6523507</v>
+        <v>6523361</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5476,6 +5466,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5502,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236876</v>
+        <v>113236967</v>
       </c>
       <c r="B48" t="n">
-        <v>93789</v>
+        <v>91344</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2810</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306543</v>
+        <v>306533</v>
       </c>
       <c r="R48" t="n">
-        <v>6523480</v>
+        <v>6523475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5578,6 +5573,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236881</v>
+        <v>113236968</v>
       </c>
       <c r="B13" t="n">
-        <v>78751</v>
+        <v>91344</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,25 +1874,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306645</v>
+        <v>306575</v>
       </c>
       <c r="R13" t="n">
-        <v>6523507</v>
+        <v>6523472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236909</v>
+        <v>113236881</v>
       </c>
       <c r="B14" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306510</v>
+        <v>306645</v>
       </c>
       <c r="R14" t="n">
-        <v>6523383</v>
+        <v>6523507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236968</v>
+        <v>113236909</v>
       </c>
       <c r="B15" t="n">
-        <v>91344</v>
+        <v>56785</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306575</v>
+        <v>306510</v>
       </c>
       <c r="R15" t="n">
-        <v>6523472</v>
+        <v>6523383</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2586,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236898</v>
+        <v>113236889</v>
       </c>
       <c r="B20" t="n">
-        <v>56769</v>
+        <v>78751</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306506</v>
+        <v>306547</v>
       </c>
       <c r="R20" t="n">
-        <v>6523348</v>
+        <v>6523388</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,11 +2662,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236889</v>
+        <v>113236887</v>
       </c>
       <c r="B21" t="n">
         <v>78751</v>
@@ -2733,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306547</v>
+        <v>306511</v>
       </c>
       <c r="R21" t="n">
-        <v>6523388</v>
+        <v>6523365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236887</v>
+        <v>113236883</v>
       </c>
       <c r="B22" t="n">
         <v>78751</v>
@@ -2835,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306511</v>
+        <v>306515</v>
       </c>
       <c r="R22" t="n">
-        <v>6523365</v>
+        <v>6523326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236883</v>
+        <v>113236898</v>
       </c>
       <c r="B23" t="n">
-        <v>78751</v>
+        <v>56769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306515</v>
+        <v>306506</v>
       </c>
       <c r="R23" t="n">
-        <v>6523326</v>
+        <v>6523348</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4564,10 +4564,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236912</v>
+        <v>113236916</v>
       </c>
       <c r="B39" t="n">
-        <v>91367</v>
+        <v>95988</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,25 +4576,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>2606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306536</v>
+        <v>306531</v>
       </c>
       <c r="R39" t="n">
-        <v>6523428</v>
+        <v>6523473</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236916</v>
+        <v>113236912</v>
       </c>
       <c r="B40" t="n">
-        <v>95988</v>
+        <v>91367</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4678,25 +4678,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306531</v>
+        <v>306536</v>
       </c>
       <c r="R40" t="n">
-        <v>6523473</v>
+        <v>6523428</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236876</v>
+        <v>113236906</v>
       </c>
       <c r="B43" t="n">
-        <v>93793</v>
+        <v>56785</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4984,25 +4984,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306543</v>
+        <v>306644</v>
       </c>
       <c r="R43" t="n">
-        <v>6523480</v>
+        <v>6523374</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5048,6 +5048,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5074,7 +5079,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236906</v>
+        <v>113236910</v>
       </c>
       <c r="B44" t="n">
         <v>56785</v>
@@ -5114,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306644</v>
+        <v>306589</v>
       </c>
       <c r="R44" t="n">
-        <v>6523374</v>
+        <v>6523472</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5181,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236910</v>
+        <v>113236876</v>
       </c>
       <c r="B45" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5193,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5221,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306589</v>
+        <v>306543</v>
       </c>
       <c r="R45" t="n">
-        <v>6523472</v>
+        <v>6523480</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5257,11 +5262,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5390,10 +5390,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236899</v>
+        <v>113236967</v>
       </c>
       <c r="B47" t="n">
-        <v>56769</v>
+        <v>91344</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5402,25 +5402,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306499</v>
+        <v>306533</v>
       </c>
       <c r="R47" t="n">
-        <v>6523361</v>
+        <v>6523475</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236967</v>
+        <v>113236899</v>
       </c>
       <c r="B48" t="n">
-        <v>91344</v>
+        <v>56769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306533</v>
+        <v>306499</v>
       </c>
       <c r="R48" t="n">
-        <v>6523475</v>
+        <v>6523361</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113198462</v>
+        <v>113198464</v>
       </c>
       <c r="B4" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306631</v>
+        <v>306551</v>
       </c>
       <c r="R4" t="n">
-        <v>6523391</v>
+        <v>6523451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1016,7 @@
         <v>113198467</v>
       </c>
       <c r="B5" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>113198463</v>
       </c>
       <c r="B6" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113198464</v>
+        <v>113198462</v>
       </c>
       <c r="B7" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306551</v>
+        <v>306631</v>
       </c>
       <c r="R7" t="n">
-        <v>6523451</v>
+        <v>6523391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236927</v>
+        <v>113236886</v>
       </c>
       <c r="B8" t="n">
-        <v>94146</v>
+        <v>78751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306474</v>
+        <v>306485</v>
       </c>
       <c r="R8" t="n">
-        <v>6523353</v>
+        <v>6523352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236903</v>
+        <v>113236894</v>
       </c>
       <c r="B9" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306590</v>
+        <v>306589</v>
       </c>
       <c r="R9" t="n">
-        <v>6523319</v>
+        <v>6523489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,11 +1514,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236904</v>
+        <v>113236926</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>91344</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306627</v>
+        <v>306544</v>
       </c>
       <c r="R10" t="n">
-        <v>6523505</v>
+        <v>6523404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,11 +1616,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236908</v>
+        <v>113236902</v>
       </c>
       <c r="B11" t="n">
         <v>56785</v>
@@ -1692,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306598</v>
+        <v>306520</v>
       </c>
       <c r="R11" t="n">
-        <v>6523398</v>
+        <v>6523332</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1722,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236911</v>
+        <v>113236909</v>
       </c>
       <c r="B12" t="n">
-        <v>96315</v>
+        <v>56785</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1761,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306509</v>
+        <v>306510</v>
       </c>
       <c r="R12" t="n">
-        <v>6523483</v>
+        <v>6523383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,13 +1827,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1862,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236968</v>
+        <v>113236895</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>78751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306575</v>
+        <v>306645</v>
       </c>
       <c r="R13" t="n">
-        <v>6523472</v>
+        <v>6523503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236881</v>
+        <v>113236908</v>
       </c>
       <c r="B14" t="n">
-        <v>78751</v>
+        <v>56785</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306645</v>
+        <v>306598</v>
       </c>
       <c r="R14" t="n">
-        <v>6523507</v>
+        <v>6523398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,6 +2034,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236909</v>
+        <v>113236876</v>
       </c>
       <c r="B15" t="n">
-        <v>56785</v>
+        <v>93793</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2077,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306510</v>
+        <v>306543</v>
       </c>
       <c r="R15" t="n">
-        <v>6523383</v>
+        <v>6523480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236882</v>
+        <v>113236925</v>
       </c>
       <c r="B16" t="n">
-        <v>78751</v>
+        <v>91344</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,25 +2179,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306556</v>
+        <v>306594</v>
       </c>
       <c r="R16" t="n">
-        <v>6523344</v>
+        <v>6523469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2269,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236892</v>
+        <v>113236885</v>
       </c>
       <c r="B17" t="n">
         <v>78751</v>
@@ -2320,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306578</v>
+        <v>306496</v>
       </c>
       <c r="R17" t="n">
-        <v>6523473</v>
+        <v>6523349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236884</v>
+        <v>113236882</v>
       </c>
       <c r="B18" t="n">
         <v>78751</v>
@@ -2422,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306508</v>
+        <v>306556</v>
       </c>
       <c r="R18" t="n">
-        <v>6523433</v>
+        <v>6523344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236877</v>
+        <v>113236927</v>
       </c>
       <c r="B19" t="n">
-        <v>93793</v>
+        <v>94146</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,21 +2489,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306513</v>
+        <v>306474</v>
       </c>
       <c r="R19" t="n">
-        <v>6523470</v>
+        <v>6523353</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236889</v>
+        <v>113236916</v>
       </c>
       <c r="B20" t="n">
-        <v>78751</v>
+        <v>95988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,25 +2587,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306547</v>
+        <v>306531</v>
       </c>
       <c r="R20" t="n">
-        <v>6523388</v>
+        <v>6523473</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236887</v>
+        <v>113236877</v>
       </c>
       <c r="B21" t="n">
-        <v>78751</v>
+        <v>93793</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,25 +2689,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306511</v>
+        <v>306513</v>
       </c>
       <c r="R21" t="n">
-        <v>6523365</v>
+        <v>6523470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236883</v>
+        <v>113236912</v>
       </c>
       <c r="B22" t="n">
-        <v>78751</v>
+        <v>91367</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2795,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306515</v>
+        <v>306536</v>
       </c>
       <c r="R22" t="n">
-        <v>6523326</v>
+        <v>6523428</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236969</v>
+        <v>113236899</v>
       </c>
       <c r="B24" t="n">
-        <v>91344</v>
+        <v>56769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,25 +3000,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306549</v>
+        <v>306499</v>
       </c>
       <c r="R24" t="n">
-        <v>6523459</v>
+        <v>6523361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3068,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236926</v>
+        <v>113236891</v>
       </c>
       <c r="B25" t="n">
-        <v>91344</v>
+        <v>78751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,25 +3107,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3146,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306544</v>
+        <v>306571</v>
       </c>
       <c r="R25" t="n">
-        <v>6523404</v>
+        <v>6523493</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236888</v>
+        <v>113236969</v>
       </c>
       <c r="B26" t="n">
-        <v>78751</v>
+        <v>91344</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3209,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306512</v>
+        <v>306549</v>
       </c>
       <c r="R26" t="n">
-        <v>6523350</v>
+        <v>6523459</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,6 +3273,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3310,10 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236896</v>
+        <v>113236911</v>
       </c>
       <c r="B27" t="n">
-        <v>56769</v>
+        <v>96315</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,25 +3316,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3350,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306488</v>
+        <v>306509</v>
       </c>
       <c r="R27" t="n">
-        <v>6523354</v>
+        <v>6523483</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,17 +3382,13 @@
           <t>2023-11-11</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3417,10 +3407,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236893</v>
+        <v>113236904</v>
       </c>
       <c r="B28" t="n">
-        <v>78751</v>
+        <v>56785</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3423,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306585</v>
+        <v>306627</v>
       </c>
       <c r="R28" t="n">
-        <v>6523469</v>
+        <v>6523505</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,6 +3483,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,7 +3514,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236907</v>
+        <v>113236905</v>
       </c>
       <c r="B29" t="n">
         <v>56785</v>
@@ -3559,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306479</v>
+        <v>306537</v>
       </c>
       <c r="R29" t="n">
-        <v>6523383</v>
+        <v>6523319</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236902</v>
+        <v>113236892</v>
       </c>
       <c r="B30" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,21 +3637,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306520</v>
+        <v>306578</v>
       </c>
       <c r="R30" t="n">
-        <v>6523332</v>
+        <v>6523473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3702,11 +3697,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,10 +3723,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236897</v>
+        <v>113236907</v>
       </c>
       <c r="B31" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,16 +3739,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3773,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306516</v>
+        <v>306479</v>
       </c>
       <c r="R31" t="n">
-        <v>6523349</v>
+        <v>6523383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,7 +3803,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236913</v>
+        <v>113236896</v>
       </c>
       <c r="B32" t="n">
-        <v>96318</v>
+        <v>56769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3852,25 +3842,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3880,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306509</v>
+        <v>306488</v>
       </c>
       <c r="R32" t="n">
-        <v>6523355</v>
+        <v>6523354</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3916,6 +3906,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,7 +3937,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236890</v>
+        <v>113236884</v>
       </c>
       <c r="B33" t="n">
         <v>78751</v>
@@ -3982,10 +3977,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306572</v>
+        <v>306508</v>
       </c>
       <c r="R33" t="n">
-        <v>6523368</v>
+        <v>6523433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,10 +4039,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236925</v>
+        <v>113236887</v>
       </c>
       <c r="B34" t="n">
-        <v>91344</v>
+        <v>78751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4051,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306594</v>
+        <v>306511</v>
       </c>
       <c r="R34" t="n">
-        <v>6523469</v>
+        <v>6523365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,10 +4141,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236905</v>
+        <v>113236889</v>
       </c>
       <c r="B35" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4162,21 +4157,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4186,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306537</v>
+        <v>306547</v>
       </c>
       <c r="R35" t="n">
-        <v>6523319</v>
+        <v>6523388</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4222,11 +4217,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4253,10 +4243,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236900</v>
+        <v>113236968</v>
       </c>
       <c r="B36" t="n">
-        <v>56769</v>
+        <v>91344</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4265,25 +4255,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4293,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306496</v>
+        <v>306575</v>
       </c>
       <c r="R36" t="n">
-        <v>6523360</v>
+        <v>6523472</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4333,7 +4323,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4360,10 +4350,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236885</v>
+        <v>113236967</v>
       </c>
       <c r="B37" t="n">
-        <v>78751</v>
+        <v>91344</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4372,25 +4362,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4400,10 +4390,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306496</v>
+        <v>306533</v>
       </c>
       <c r="R37" t="n">
-        <v>6523349</v>
+        <v>6523475</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4436,6 +4426,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4462,10 +4457,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236894</v>
+        <v>113236913</v>
       </c>
       <c r="B38" t="n">
-        <v>78751</v>
+        <v>96318</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,25 +4469,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306589</v>
+        <v>306509</v>
       </c>
       <c r="R38" t="n">
-        <v>6523489</v>
+        <v>6523355</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4564,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236916</v>
+        <v>113236897</v>
       </c>
       <c r="B39" t="n">
-        <v>95988</v>
+        <v>56769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4576,25 +4571,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4604,10 +4599,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306531</v>
+        <v>306516</v>
       </c>
       <c r="R39" t="n">
-        <v>6523473</v>
+        <v>6523349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4640,6 +4635,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236912</v>
+        <v>113236893</v>
       </c>
       <c r="B40" t="n">
-        <v>91367</v>
+        <v>78751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,21 +4682,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306536</v>
+        <v>306585</v>
       </c>
       <c r="R40" t="n">
-        <v>6523428</v>
+        <v>6523469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236891</v>
+        <v>113236888</v>
       </c>
       <c r="B41" t="n">
         <v>78751</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306571</v>
+        <v>306512</v>
       </c>
       <c r="R41" t="n">
-        <v>6523493</v>
+        <v>6523350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236886</v>
+        <v>113236883</v>
       </c>
       <c r="B42" t="n">
         <v>78751</v>
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306485</v>
+        <v>306515</v>
       </c>
       <c r="R42" t="n">
-        <v>6523352</v>
+        <v>6523326</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,7 +4972,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236906</v>
+        <v>113236903</v>
       </c>
       <c r="B43" t="n">
         <v>56785</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306644</v>
+        <v>306590</v>
       </c>
       <c r="R43" t="n">
-        <v>6523374</v>
+        <v>6523319</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236876</v>
+        <v>113236881</v>
       </c>
       <c r="B45" t="n">
-        <v>93793</v>
+        <v>78751</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5198,25 +5198,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306543</v>
+        <v>306645</v>
       </c>
       <c r="R45" t="n">
-        <v>6523480</v>
+        <v>6523507</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236895</v>
+        <v>113236900</v>
       </c>
       <c r="B46" t="n">
-        <v>78751</v>
+        <v>56769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,21 +5304,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306645</v>
+        <v>306496</v>
       </c>
       <c r="R46" t="n">
-        <v>6523503</v>
+        <v>6523360</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5364,6 +5364,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5390,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236967</v>
+        <v>113236906</v>
       </c>
       <c r="B47" t="n">
-        <v>91344</v>
+        <v>56785</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5402,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5430,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306533</v>
+        <v>306644</v>
       </c>
       <c r="R47" t="n">
-        <v>6523475</v>
+        <v>6523374</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5470,7 +5475,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236899</v>
+        <v>113236890</v>
       </c>
       <c r="B48" t="n">
-        <v>56769</v>
+        <v>78751</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5518,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306499</v>
+        <v>306572</v>
       </c>
       <c r="R48" t="n">
-        <v>6523361</v>
+        <v>6523368</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5573,11 +5578,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236886</v>
+        <v>113236913</v>
       </c>
       <c r="B8" t="n">
-        <v>78751</v>
+        <v>96324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306485</v>
+        <v>306509</v>
       </c>
       <c r="R8" t="n">
-        <v>6523352</v>
+        <v>6523355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1441,7 @@
         <v>113236894</v>
       </c>
       <c r="B9" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236926</v>
+        <v>113236898</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>56773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306544</v>
+        <v>306506</v>
       </c>
       <c r="R10" t="n">
-        <v>6523404</v>
+        <v>6523348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1616,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236902</v>
+        <v>113236900</v>
       </c>
       <c r="B11" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,16 +1663,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1682,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306520</v>
+        <v>306496</v>
       </c>
       <c r="R11" t="n">
-        <v>6523332</v>
+        <v>6523360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236909</v>
+        <v>113236881</v>
       </c>
       <c r="B12" t="n">
-        <v>56785</v>
+        <v>78757</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306510</v>
+        <v>306645</v>
       </c>
       <c r="R12" t="n">
-        <v>6523383</v>
+        <v>6523507</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,11 +1830,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236895</v>
+        <v>113236925</v>
       </c>
       <c r="B13" t="n">
-        <v>78751</v>
+        <v>91350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306645</v>
+        <v>306594</v>
       </c>
       <c r="R13" t="n">
-        <v>6523503</v>
+        <v>6523469</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236908</v>
+        <v>113236891</v>
       </c>
       <c r="B14" t="n">
-        <v>56785</v>
+        <v>78757</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306598</v>
+        <v>306571</v>
       </c>
       <c r="R14" t="n">
-        <v>6523398</v>
+        <v>6523493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,11 +2034,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236876</v>
+        <v>113236903</v>
       </c>
       <c r="B15" t="n">
-        <v>93793</v>
+        <v>56789</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,25 +2072,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306543</v>
+        <v>306590</v>
       </c>
       <c r="R15" t="n">
-        <v>6523480</v>
+        <v>6523319</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,6 +2136,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236925</v>
+        <v>113236902</v>
       </c>
       <c r="B16" t="n">
-        <v>91344</v>
+        <v>56789</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2179,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306594</v>
+        <v>306520</v>
       </c>
       <c r="R16" t="n">
-        <v>6523469</v>
+        <v>6523332</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,6 +2243,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236885</v>
+        <v>113236968</v>
       </c>
       <c r="B17" t="n">
-        <v>78751</v>
+        <v>91350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,25 +2286,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306496</v>
+        <v>306575</v>
       </c>
       <c r="R17" t="n">
-        <v>6523349</v>
+        <v>6523472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,6 +2350,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236882</v>
+        <v>113236893</v>
       </c>
       <c r="B18" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306556</v>
+        <v>306585</v>
       </c>
       <c r="R18" t="n">
-        <v>6523344</v>
+        <v>6523469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236927</v>
+        <v>113236905</v>
       </c>
       <c r="B19" t="n">
-        <v>94146</v>
+        <v>56789</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,25 +2495,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2513,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306474</v>
+        <v>306537</v>
       </c>
       <c r="R19" t="n">
-        <v>6523353</v>
+        <v>6523319</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,6 +2559,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236916</v>
+        <v>113236896</v>
       </c>
       <c r="B20" t="n">
-        <v>95988</v>
+        <v>56773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,25 +2602,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2615,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306531</v>
+        <v>306488</v>
       </c>
       <c r="R20" t="n">
-        <v>6523473</v>
+        <v>6523354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,6 +2666,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2677,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236877</v>
+        <v>113236911</v>
       </c>
       <c r="B21" t="n">
-        <v>93793</v>
+        <v>96321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,21 +2713,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2717,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306513</v>
+        <v>306509</v>
       </c>
       <c r="R21" t="n">
-        <v>6523470</v>
+        <v>6523483</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,6 +2781,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2779,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236912</v>
+        <v>113236876</v>
       </c>
       <c r="B22" t="n">
-        <v>91367</v>
+        <v>93799</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2819,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306536</v>
+        <v>306543</v>
       </c>
       <c r="R22" t="n">
-        <v>6523428</v>
+        <v>6523480</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236898</v>
+        <v>113236969</v>
       </c>
       <c r="B23" t="n">
-        <v>56769</v>
+        <v>91350</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,25 +2914,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2921,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306506</v>
+        <v>306549</v>
       </c>
       <c r="R23" t="n">
-        <v>6523348</v>
+        <v>6523459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,7 +2982,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2988,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236899</v>
+        <v>113236916</v>
       </c>
       <c r="B24" t="n">
-        <v>56769</v>
+        <v>95994</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,25 +3021,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3028,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306499</v>
+        <v>306531</v>
       </c>
       <c r="R24" t="n">
-        <v>6523361</v>
+        <v>6523473</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,11 +3085,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3095,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236891</v>
+        <v>113236906</v>
       </c>
       <c r="B25" t="n">
-        <v>78751</v>
+        <v>56789</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306571</v>
+        <v>306644</v>
       </c>
       <c r="R25" t="n">
-        <v>6523493</v>
+        <v>6523374</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3197,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236969</v>
+        <v>113236927</v>
       </c>
       <c r="B26" t="n">
-        <v>91344</v>
+        <v>94152</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306549</v>
+        <v>306474</v>
       </c>
       <c r="R26" t="n">
-        <v>6523459</v>
+        <v>6523353</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3304,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236911</v>
+        <v>113236883</v>
       </c>
       <c r="B27" t="n">
-        <v>96315</v>
+        <v>78757</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3316,25 +3332,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3344,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306509</v>
+        <v>306515</v>
       </c>
       <c r="R27" t="n">
-        <v>6523483</v>
+        <v>6523326</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3404,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3407,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236904</v>
+        <v>113236907</v>
       </c>
       <c r="B28" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306627</v>
+        <v>306479</v>
       </c>
       <c r="R28" t="n">
-        <v>6523505</v>
+        <v>6523383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3514,10 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236905</v>
+        <v>113236895</v>
       </c>
       <c r="B29" t="n">
-        <v>56785</v>
+        <v>78757</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3530,21 +3545,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3569,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306537</v>
+        <v>306645</v>
       </c>
       <c r="R29" t="n">
-        <v>6523319</v>
+        <v>6523503</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,11 +3605,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,10 +3631,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236892</v>
+        <v>113236897</v>
       </c>
       <c r="B30" t="n">
-        <v>78751</v>
+        <v>56773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3637,21 +3647,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3671,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306578</v>
+        <v>306516</v>
       </c>
       <c r="R30" t="n">
-        <v>6523473</v>
+        <v>6523349</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,6 +3707,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236907</v>
+        <v>113236886</v>
       </c>
       <c r="B31" t="n">
-        <v>56785</v>
+        <v>78757</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3739,21 +3754,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3763,10 +3778,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306479</v>
+        <v>306485</v>
       </c>
       <c r="R31" t="n">
-        <v>6523383</v>
+        <v>6523352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,11 +3814,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3830,10 +3840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236896</v>
+        <v>113236904</v>
       </c>
       <c r="B32" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3846,16 +3856,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3870,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306488</v>
+        <v>306627</v>
       </c>
       <c r="R32" t="n">
-        <v>6523354</v>
+        <v>6523505</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3910,7 +3920,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,10 +3947,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236884</v>
+        <v>113236889</v>
       </c>
       <c r="B33" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3977,10 +3987,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306508</v>
+        <v>306547</v>
       </c>
       <c r="R33" t="n">
-        <v>6523433</v>
+        <v>6523388</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,10 +4049,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236887</v>
+        <v>113236892</v>
       </c>
       <c r="B34" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4079,10 +4089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306511</v>
+        <v>306578</v>
       </c>
       <c r="R34" t="n">
-        <v>6523365</v>
+        <v>6523473</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236889</v>
+        <v>113236926</v>
       </c>
       <c r="B35" t="n">
-        <v>78751</v>
+        <v>91350</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4153,25 +4163,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306547</v>
+        <v>306544</v>
       </c>
       <c r="R35" t="n">
-        <v>6523388</v>
+        <v>6523404</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4243,10 +4253,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236968</v>
+        <v>113236967</v>
       </c>
       <c r="B36" t="n">
-        <v>91344</v>
+        <v>91350</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4283,10 +4293,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306575</v>
+        <v>306533</v>
       </c>
       <c r="R36" t="n">
-        <v>6523472</v>
+        <v>6523475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4323,7 +4333,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,10 +4360,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236967</v>
+        <v>113236908</v>
       </c>
       <c r="B37" t="n">
-        <v>91344</v>
+        <v>56789</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4362,25 +4372,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4390,10 +4400,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306533</v>
+        <v>306598</v>
       </c>
       <c r="R37" t="n">
-        <v>6523475</v>
+        <v>6523398</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4430,7 +4440,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>13 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236913</v>
+        <v>113236890</v>
       </c>
       <c r="B38" t="n">
-        <v>96318</v>
+        <v>78757</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4469,25 +4479,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4497,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306509</v>
+        <v>306572</v>
       </c>
       <c r="R38" t="n">
-        <v>6523355</v>
+        <v>6523368</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4559,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236897</v>
+        <v>113236885</v>
       </c>
       <c r="B39" t="n">
-        <v>56769</v>
+        <v>78757</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4575,21 +4585,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4599,7 +4609,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306516</v>
+        <v>306496</v>
       </c>
       <c r="R39" t="n">
         <v>6523349</v>
@@ -4635,11 +4645,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4666,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236893</v>
+        <v>113236910</v>
       </c>
       <c r="B40" t="n">
-        <v>78751</v>
+        <v>56789</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4706,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306585</v>
+        <v>306589</v>
       </c>
       <c r="R40" t="n">
-        <v>6523469</v>
+        <v>6523472</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4742,6 +4747,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4768,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236888</v>
+        <v>113236912</v>
       </c>
       <c r="B41" t="n">
-        <v>78751</v>
+        <v>91373</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,21 +4794,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4808,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306512</v>
+        <v>306536</v>
       </c>
       <c r="R41" t="n">
-        <v>6523350</v>
+        <v>6523428</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,10 +4880,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236883</v>
+        <v>113236884</v>
       </c>
       <c r="B42" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4910,10 +4920,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306515</v>
+        <v>306508</v>
       </c>
       <c r="R42" t="n">
-        <v>6523326</v>
+        <v>6523433</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4972,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236903</v>
+        <v>113236899</v>
       </c>
       <c r="B43" t="n">
-        <v>56785</v>
+        <v>56773</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,16 +4998,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5012,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306590</v>
+        <v>306499</v>
       </c>
       <c r="R43" t="n">
-        <v>6523319</v>
+        <v>6523361</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236910</v>
+        <v>113236887</v>
       </c>
       <c r="B44" t="n">
-        <v>56785</v>
+        <v>78757</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,21 +5105,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306589</v>
+        <v>306511</v>
       </c>
       <c r="R44" t="n">
-        <v>6523472</v>
+        <v>6523365</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5155,11 +5165,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5186,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236881</v>
+        <v>113236888</v>
       </c>
       <c r="B45" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5226,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306645</v>
+        <v>306512</v>
       </c>
       <c r="R45" t="n">
-        <v>6523507</v>
+        <v>6523350</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236900</v>
+        <v>113236909</v>
       </c>
       <c r="B46" t="n">
-        <v>56769</v>
+        <v>56789</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,16 +5309,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5328,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306496</v>
+        <v>306510</v>
       </c>
       <c r="R46" t="n">
-        <v>6523360</v>
+        <v>6523383</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5368,7 +5373,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5395,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236906</v>
+        <v>113236877</v>
       </c>
       <c r="B47" t="n">
-        <v>56785</v>
+        <v>93799</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,25 +5412,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306644</v>
+        <v>306513</v>
       </c>
       <c r="R47" t="n">
-        <v>6523374</v>
+        <v>6523470</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,11 +5476,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236890</v>
+        <v>113236882</v>
       </c>
       <c r="B48" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306572</v>
+        <v>306556</v>
       </c>
       <c r="R48" t="n">
-        <v>6523368</v>
+        <v>6523344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236913</v>
+        <v>113236884</v>
       </c>
       <c r="B8" t="n">
-        <v>96324</v>
+        <v>78757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,25 +1348,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306509</v>
+        <v>306508</v>
       </c>
       <c r="R8" t="n">
-        <v>6523355</v>
+        <v>6523433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236894</v>
+        <v>113236889</v>
       </c>
       <c r="B9" t="n">
         <v>78757</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306589</v>
+        <v>306547</v>
       </c>
       <c r="R9" t="n">
-        <v>6523489</v>
+        <v>6523388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236898</v>
+        <v>113236927</v>
       </c>
       <c r="B10" t="n">
-        <v>56773</v>
+        <v>94152</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1552,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306506</v>
+        <v>306474</v>
       </c>
       <c r="R10" t="n">
-        <v>6523348</v>
+        <v>6523353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,11 +1616,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236900</v>
+        <v>113236906</v>
       </c>
       <c r="B11" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,16 +1658,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306496</v>
+        <v>306644</v>
       </c>
       <c r="R11" t="n">
-        <v>6523360</v>
+        <v>6523374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1722,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236881</v>
+        <v>113236911</v>
       </c>
       <c r="B12" t="n">
-        <v>78757</v>
+        <v>96321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,25 +1761,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306645</v>
+        <v>306509</v>
       </c>
       <c r="R12" t="n">
-        <v>6523507</v>
+        <v>6523483</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,6 +1833,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1856,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236925</v>
+        <v>113236912</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1864,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306594</v>
+        <v>306536</v>
       </c>
       <c r="R13" t="n">
-        <v>6523469</v>
+        <v>6523428</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236891</v>
+        <v>113236876</v>
       </c>
       <c r="B14" t="n">
-        <v>78757</v>
+        <v>93799</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,25 +1966,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306571</v>
+        <v>306543</v>
       </c>
       <c r="R14" t="n">
-        <v>6523493</v>
+        <v>6523480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236902</v>
+        <v>113236916</v>
       </c>
       <c r="B16" t="n">
-        <v>56789</v>
+        <v>95994</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2175,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306520</v>
+        <v>306531</v>
       </c>
       <c r="R16" t="n">
-        <v>6523332</v>
+        <v>6523473</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,11 +2239,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236968</v>
+        <v>113236900</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>56773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306575</v>
+        <v>306496</v>
       </c>
       <c r="R17" t="n">
-        <v>6523472</v>
+        <v>6523360</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>8 fruktkroppar</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236893</v>
+        <v>113236898</v>
       </c>
       <c r="B18" t="n">
-        <v>78757</v>
+        <v>56773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306585</v>
+        <v>306506</v>
       </c>
       <c r="R18" t="n">
-        <v>6523469</v>
+        <v>6523348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236905</v>
+        <v>113236888</v>
       </c>
       <c r="B19" t="n">
-        <v>56789</v>
+        <v>78757</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306537</v>
+        <v>306512</v>
       </c>
       <c r="R19" t="n">
-        <v>6523319</v>
+        <v>6523350</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,11 +2555,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236896</v>
+        <v>113236904</v>
       </c>
       <c r="B20" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,16 +2597,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2630,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306488</v>
+        <v>306627</v>
       </c>
       <c r="R20" t="n">
-        <v>6523354</v>
+        <v>6523505</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236911</v>
+        <v>113236896</v>
       </c>
       <c r="B21" t="n">
-        <v>96321</v>
+        <v>56773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,25 +2700,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306509</v>
+        <v>306488</v>
       </c>
       <c r="R21" t="n">
-        <v>6523483</v>
+        <v>6523354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,13 +2766,17 @@
           <t>2023-11-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2800,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236876</v>
+        <v>113236894</v>
       </c>
       <c r="B22" t="n">
-        <v>93799</v>
+        <v>78757</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306543</v>
+        <v>306589</v>
       </c>
       <c r="R22" t="n">
-        <v>6523480</v>
+        <v>6523489</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2902,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236969</v>
+        <v>113236891</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>78757</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2914,25 +2909,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306549</v>
+        <v>306571</v>
       </c>
       <c r="R23" t="n">
-        <v>6523459</v>
+        <v>6523493</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,11 +2973,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236916</v>
+        <v>113236887</v>
       </c>
       <c r="B24" t="n">
-        <v>95994</v>
+        <v>78757</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3021,25 +3011,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306531</v>
+        <v>306511</v>
       </c>
       <c r="R24" t="n">
-        <v>6523473</v>
+        <v>6523365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,7 +3101,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236906</v>
+        <v>113236910</v>
       </c>
       <c r="B25" t="n">
         <v>56789</v>
@@ -3151,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306644</v>
+        <v>306589</v>
       </c>
       <c r="R25" t="n">
-        <v>6523374</v>
+        <v>6523472</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236927</v>
+        <v>113236877</v>
       </c>
       <c r="B26" t="n">
-        <v>94152</v>
+        <v>93799</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3224,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3248,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306474</v>
+        <v>306513</v>
       </c>
       <c r="R26" t="n">
-        <v>6523353</v>
+        <v>6523470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3310,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236883</v>
+        <v>113236925</v>
       </c>
       <c r="B27" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,25 +3322,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3360,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306515</v>
+        <v>306594</v>
       </c>
       <c r="R27" t="n">
-        <v>6523326</v>
+        <v>6523469</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3412,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236907</v>
+        <v>113236886</v>
       </c>
       <c r="B28" t="n">
-        <v>56789</v>
+        <v>78757</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,21 +3428,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3462,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306479</v>
+        <v>306485</v>
       </c>
       <c r="R28" t="n">
-        <v>6523383</v>
+        <v>6523352</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3498,11 +3488,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3529,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236895</v>
+        <v>113236969</v>
       </c>
       <c r="B29" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3541,25 +3526,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3569,10 +3554,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306645</v>
+        <v>306549</v>
       </c>
       <c r="R29" t="n">
-        <v>6523503</v>
+        <v>6523459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,6 +3590,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3621,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236897</v>
+        <v>113236902</v>
       </c>
       <c r="B30" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3647,16 +3637,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3671,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306516</v>
+        <v>306520</v>
       </c>
       <c r="R30" t="n">
-        <v>6523349</v>
+        <v>6523332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3738,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236886</v>
+        <v>113236897</v>
       </c>
       <c r="B31" t="n">
-        <v>78757</v>
+        <v>56773</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3754,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3778,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306485</v>
+        <v>306516</v>
       </c>
       <c r="R31" t="n">
-        <v>6523352</v>
+        <v>6523349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3814,6 +3804,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3840,7 +3835,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236904</v>
+        <v>113236905</v>
       </c>
       <c r="B32" t="n">
         <v>56789</v>
@@ -3880,10 +3875,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306627</v>
+        <v>306537</v>
       </c>
       <c r="R32" t="n">
-        <v>6523505</v>
+        <v>6523319</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,10 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236889</v>
+        <v>113236913</v>
       </c>
       <c r="B33" t="n">
-        <v>78757</v>
+        <v>96324</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3959,25 +3954,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3987,10 +3982,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306547</v>
+        <v>306509</v>
       </c>
       <c r="R33" t="n">
-        <v>6523388</v>
+        <v>6523355</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4049,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236892</v>
+        <v>113236968</v>
       </c>
       <c r="B34" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4061,25 +4056,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4089,10 +4084,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306578</v>
+        <v>306575</v>
       </c>
       <c r="R34" t="n">
-        <v>6523473</v>
+        <v>6523472</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4125,6 +4120,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236926</v>
+        <v>113236907</v>
       </c>
       <c r="B35" t="n">
-        <v>91350</v>
+        <v>56789</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4163,25 +4163,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306544</v>
+        <v>306479</v>
       </c>
       <c r="R35" t="n">
-        <v>6523404</v>
+        <v>6523383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,6 +4227,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4253,10 +4258,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236967</v>
+        <v>113236895</v>
       </c>
       <c r="B36" t="n">
-        <v>91350</v>
+        <v>78757</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4265,25 +4270,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4293,10 +4298,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306533</v>
+        <v>306645</v>
       </c>
       <c r="R36" t="n">
-        <v>6523475</v>
+        <v>6523503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4329,11 +4334,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4360,7 +4360,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236908</v>
+        <v>113236909</v>
       </c>
       <c r="B37" t="n">
         <v>56789</v>
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306598</v>
+        <v>306510</v>
       </c>
       <c r="R37" t="n">
-        <v>6523398</v>
+        <v>6523383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236890</v>
+        <v>113236926</v>
       </c>
       <c r="B38" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,25 +4479,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306572</v>
+        <v>306544</v>
       </c>
       <c r="R38" t="n">
-        <v>6523368</v>
+        <v>6523404</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236885</v>
+        <v>113236882</v>
       </c>
       <c r="B39" t="n">
         <v>78757</v>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306496</v>
+        <v>306556</v>
       </c>
       <c r="R39" t="n">
-        <v>6523349</v>
+        <v>6523344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236910</v>
+        <v>113236908</v>
       </c>
       <c r="B40" t="n">
         <v>56789</v>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306589</v>
+        <v>306598</v>
       </c>
       <c r="R40" t="n">
-        <v>6523472</v>
+        <v>6523398</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236912</v>
+        <v>113236899</v>
       </c>
       <c r="B41" t="n">
-        <v>91373</v>
+        <v>56773</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,21 +4794,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306536</v>
+        <v>306499</v>
       </c>
       <c r="R41" t="n">
-        <v>6523428</v>
+        <v>6523361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4854,6 +4854,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4880,7 +4885,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236884</v>
+        <v>113236883</v>
       </c>
       <c r="B42" t="n">
         <v>78757</v>
@@ -4920,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306508</v>
+        <v>306515</v>
       </c>
       <c r="R42" t="n">
-        <v>6523433</v>
+        <v>6523326</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236899</v>
+        <v>113236892</v>
       </c>
       <c r="B43" t="n">
-        <v>56773</v>
+        <v>78757</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5022,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306499</v>
+        <v>306578</v>
       </c>
       <c r="R43" t="n">
-        <v>6523361</v>
+        <v>6523473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5058,11 +5063,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,7 +5089,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236887</v>
+        <v>113236881</v>
       </c>
       <c r="B44" t="n">
         <v>78757</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306511</v>
+        <v>306645</v>
       </c>
       <c r="R44" t="n">
-        <v>6523365</v>
+        <v>6523507</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236888</v>
+        <v>113236885</v>
       </c>
       <c r="B45" t="n">
         <v>78757</v>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306512</v>
+        <v>306496</v>
       </c>
       <c r="R45" t="n">
-        <v>6523350</v>
+        <v>6523349</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236909</v>
+        <v>113236890</v>
       </c>
       <c r="B46" t="n">
-        <v>56789</v>
+        <v>78757</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306510</v>
+        <v>306572</v>
       </c>
       <c r="R46" t="n">
-        <v>6523383</v>
+        <v>6523368</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5369,11 +5369,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5400,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236877</v>
+        <v>113236893</v>
       </c>
       <c r="B47" t="n">
-        <v>93799</v>
+        <v>78757</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306513</v>
+        <v>306585</v>
       </c>
       <c r="R47" t="n">
-        <v>6523470</v>
+        <v>6523469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236882</v>
+        <v>113236967</v>
       </c>
       <c r="B48" t="n">
-        <v>78757</v>
+        <v>91350</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306556</v>
+        <v>306533</v>
       </c>
       <c r="R48" t="n">
-        <v>6523344</v>
+        <v>6523475</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5578,6 +5573,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113236884</v>
+        <v>113236891</v>
       </c>
       <c r="B8" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306508</v>
+        <v>306571</v>
       </c>
       <c r="R8" t="n">
-        <v>6523433</v>
+        <v>6523493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113236889</v>
+        <v>113236909</v>
       </c>
       <c r="B9" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306547</v>
+        <v>306510</v>
       </c>
       <c r="R9" t="n">
-        <v>6523388</v>
+        <v>6523383</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113236927</v>
+        <v>113236892</v>
       </c>
       <c r="B10" t="n">
-        <v>94152</v>
+        <v>78764</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,25 +1557,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306474</v>
+        <v>306578</v>
       </c>
       <c r="R10" t="n">
-        <v>6523353</v>
+        <v>6523473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113236906</v>
+        <v>113236887</v>
       </c>
       <c r="B11" t="n">
-        <v>56789</v>
+        <v>78764</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306644</v>
+        <v>306511</v>
       </c>
       <c r="R11" t="n">
-        <v>6523374</v>
+        <v>6523365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,11 +1723,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113236911</v>
+        <v>113236927</v>
       </c>
       <c r="B12" t="n">
-        <v>96321</v>
+        <v>94159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306509</v>
+        <v>306474</v>
       </c>
       <c r="R12" t="n">
-        <v>6523483</v>
+        <v>6523353</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1852,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113236912</v>
+        <v>113236881</v>
       </c>
       <c r="B13" t="n">
-        <v>91373</v>
+        <v>78764</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306536</v>
+        <v>306645</v>
       </c>
       <c r="R13" t="n">
-        <v>6523428</v>
+        <v>6523507</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113236876</v>
+        <v>113236883</v>
       </c>
       <c r="B14" t="n">
-        <v>93799</v>
+        <v>78764</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1965,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306543</v>
+        <v>306515</v>
       </c>
       <c r="R14" t="n">
-        <v>6523480</v>
+        <v>6523326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113236903</v>
+        <v>113236889</v>
       </c>
       <c r="B15" t="n">
-        <v>56789</v>
+        <v>78764</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306590</v>
+        <v>306547</v>
       </c>
       <c r="R15" t="n">
-        <v>6523319</v>
+        <v>6523388</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2131,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113236916</v>
+        <v>113236886</v>
       </c>
       <c r="B16" t="n">
-        <v>95994</v>
+        <v>78764</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,25 +2169,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306531</v>
+        <v>306485</v>
       </c>
       <c r="R16" t="n">
-        <v>6523473</v>
+        <v>6523352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113236900</v>
+        <v>113236882</v>
       </c>
       <c r="B17" t="n">
-        <v>56773</v>
+        <v>78764</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>306496</v>
+        <v>306556</v>
       </c>
       <c r="R17" t="n">
-        <v>6523360</v>
+        <v>6523344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,11 +2335,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113236898</v>
+        <v>113236906</v>
       </c>
       <c r="B18" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,16 +2377,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2412,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>306506</v>
+        <v>306644</v>
       </c>
       <c r="R18" t="n">
-        <v>6523348</v>
+        <v>6523374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2441,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,10 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113236888</v>
+        <v>113236910</v>
       </c>
       <c r="B19" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2495,21 +2484,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>306512</v>
+        <v>306589</v>
       </c>
       <c r="R19" t="n">
-        <v>6523350</v>
+        <v>6523472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,6 +2544,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113236904</v>
+        <v>113236903</v>
       </c>
       <c r="B20" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2621,10 +2615,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>306627</v>
+        <v>306590</v>
       </c>
       <c r="R20" t="n">
-        <v>6523505</v>
+        <v>6523319</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2655,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113236896</v>
+        <v>113236898</v>
       </c>
       <c r="B21" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,10 +2722,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>306488</v>
+        <v>306506</v>
       </c>
       <c r="R21" t="n">
-        <v>6523354</v>
+        <v>6523348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2789,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113236894</v>
+        <v>113236912</v>
       </c>
       <c r="B22" t="n">
-        <v>78757</v>
+        <v>91380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2805,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2829,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>306589</v>
+        <v>306536</v>
       </c>
       <c r="R22" t="n">
-        <v>6523489</v>
+        <v>6523428</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2897,10 +2891,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113236891</v>
+        <v>113236876</v>
       </c>
       <c r="B23" t="n">
-        <v>78757</v>
+        <v>93806</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2909,25 +2903,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>306571</v>
+        <v>306543</v>
       </c>
       <c r="R23" t="n">
-        <v>6523493</v>
+        <v>6523480</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,10 +2993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113236887</v>
+        <v>113236968</v>
       </c>
       <c r="B24" t="n">
-        <v>78757</v>
+        <v>91357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3011,25 +3005,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>306511</v>
+        <v>306575</v>
       </c>
       <c r="R24" t="n">
-        <v>6523365</v>
+        <v>6523472</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3069,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3101,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113236910</v>
+        <v>113236890</v>
       </c>
       <c r="B25" t="n">
-        <v>56789</v>
+        <v>78764</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,21 +3116,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>306589</v>
+        <v>306572</v>
       </c>
       <c r="R25" t="n">
-        <v>6523472</v>
+        <v>6523368</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3177,11 +3176,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3208,10 +3202,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113236877</v>
+        <v>113236884</v>
       </c>
       <c r="B26" t="n">
-        <v>93799</v>
+        <v>78764</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,25 +3214,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2810</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3248,10 +3242,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>306513</v>
+        <v>306508</v>
       </c>
       <c r="R26" t="n">
-        <v>6523470</v>
+        <v>6523433</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113236925</v>
+        <v>113236926</v>
       </c>
       <c r="B27" t="n">
-        <v>91350</v>
+        <v>91357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,10 +3344,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>306594</v>
+        <v>306544</v>
       </c>
       <c r="R27" t="n">
-        <v>6523469</v>
+        <v>6523404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3412,10 +3406,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113236886</v>
+        <v>113236902</v>
       </c>
       <c r="B28" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3428,21 +3422,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3452,10 +3446,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>306485</v>
+        <v>306520</v>
       </c>
       <c r="R28" t="n">
-        <v>6523352</v>
+        <v>6523332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,6 +3482,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113236969</v>
+        <v>113236907</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>56796</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,25 +3525,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3554,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>306549</v>
+        <v>306479</v>
       </c>
       <c r="R29" t="n">
-        <v>6523459</v>
+        <v>6523383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3594,7 +3593,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3621,10 +3620,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113236902</v>
+        <v>113236916</v>
       </c>
       <c r="B30" t="n">
-        <v>56789</v>
+        <v>96001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3633,25 +3632,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3661,10 +3660,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>306520</v>
+        <v>306531</v>
       </c>
       <c r="R30" t="n">
-        <v>6523332</v>
+        <v>6523473</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,11 +3696,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,10 +3722,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113236897</v>
+        <v>113236888</v>
       </c>
       <c r="B31" t="n">
-        <v>56773</v>
+        <v>78764</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3744,21 +3738,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3768,10 +3762,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>306516</v>
+        <v>306512</v>
       </c>
       <c r="R31" t="n">
-        <v>6523349</v>
+        <v>6523350</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3804,11 +3798,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113236905</v>
+        <v>113236900</v>
       </c>
       <c r="B32" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,16 +3840,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3875,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>306537</v>
+        <v>306496</v>
       </c>
       <c r="R32" t="n">
-        <v>6523319</v>
+        <v>6523360</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,7 +3904,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3942,10 +3931,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113236913</v>
+        <v>113236925</v>
       </c>
       <c r="B33" t="n">
-        <v>96324</v>
+        <v>91357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,21 +3947,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3982,10 +3971,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>306509</v>
+        <v>306594</v>
       </c>
       <c r="R33" t="n">
-        <v>6523355</v>
+        <v>6523469</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,10 +4033,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113236968</v>
+        <v>113236895</v>
       </c>
       <c r="B34" t="n">
-        <v>91350</v>
+        <v>78764</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4056,25 +4045,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4084,10 +4073,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>306575</v>
+        <v>306645</v>
       </c>
       <c r="R34" t="n">
-        <v>6523472</v>
+        <v>6523503</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4120,11 +4109,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>8 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4151,10 +4135,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113236907</v>
+        <v>113236877</v>
       </c>
       <c r="B35" t="n">
-        <v>56789</v>
+        <v>93806</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4163,25 +4147,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4191,10 +4175,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>306479</v>
+        <v>306513</v>
       </c>
       <c r="R35" t="n">
-        <v>6523383</v>
+        <v>6523470</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,11 +4211,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,10 +4237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113236895</v>
+        <v>113236967</v>
       </c>
       <c r="B36" t="n">
-        <v>78757</v>
+        <v>91357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,25 +4249,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4298,10 +4277,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>306645</v>
+        <v>306533</v>
       </c>
       <c r="R36" t="n">
-        <v>6523503</v>
+        <v>6523475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4334,6 +4313,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4360,10 +4344,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113236909</v>
+        <v>113236908</v>
       </c>
       <c r="B37" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4400,10 +4384,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>306510</v>
+        <v>306598</v>
       </c>
       <c r="R37" t="n">
-        <v>6523383</v>
+        <v>6523398</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4451,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113236926</v>
+        <v>113236899</v>
       </c>
       <c r="B38" t="n">
-        <v>91350</v>
+        <v>56780</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,25 +4463,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4491,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>306544</v>
+        <v>306499</v>
       </c>
       <c r="R38" t="n">
-        <v>6523404</v>
+        <v>6523361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4543,6 +4527,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4569,10 +4558,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113236882</v>
+        <v>113236904</v>
       </c>
       <c r="B39" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4585,21 +4574,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4609,10 +4598,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>306556</v>
+        <v>306627</v>
       </c>
       <c r="R39" t="n">
-        <v>6523344</v>
+        <v>6523505</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4645,6 +4634,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,10 +4665,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113236908</v>
+        <v>113236896</v>
       </c>
       <c r="B40" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,16 +4681,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4711,10 +4705,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>306598</v>
+        <v>306488</v>
       </c>
       <c r="R40" t="n">
-        <v>6523398</v>
+        <v>6523354</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,7 +4745,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4778,10 +4772,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113236899</v>
+        <v>113236897</v>
       </c>
       <c r="B41" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,10 +4812,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>306499</v>
+        <v>306516</v>
       </c>
       <c r="R41" t="n">
-        <v>6523361</v>
+        <v>6523349</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,10 +4879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113236883</v>
+        <v>113236911</v>
       </c>
       <c r="B42" t="n">
-        <v>78757</v>
+        <v>96328</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,25 +4891,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4919,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>306515</v>
+        <v>306509</v>
       </c>
       <c r="R42" t="n">
-        <v>6523326</v>
+        <v>6523483</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4969,6 +4963,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4987,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236892</v>
+        <v>113236885</v>
       </c>
       <c r="B43" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>306578</v>
+        <v>306496</v>
       </c>
       <c r="R43" t="n">
-        <v>6523473</v>
+        <v>6523349</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,10 +5084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236881</v>
+        <v>113236894</v>
       </c>
       <c r="B44" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5129,10 +5124,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>306645</v>
+        <v>306589</v>
       </c>
       <c r="R44" t="n">
-        <v>6523507</v>
+        <v>6523489</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5186,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236885</v>
+        <v>113236905</v>
       </c>
       <c r="B45" t="n">
-        <v>78757</v>
+        <v>56796</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5207,21 +5202,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>306496</v>
+        <v>306537</v>
       </c>
       <c r="R45" t="n">
-        <v>6523349</v>
+        <v>6523319</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5267,6 +5262,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113236890</v>
+        <v>113236913</v>
       </c>
       <c r="B46" t="n">
-        <v>78757</v>
+        <v>96331</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>306572</v>
+        <v>306509</v>
       </c>
       <c r="R46" t="n">
-        <v>6523368</v>
+        <v>6523355</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113236893</v>
+        <v>113236969</v>
       </c>
       <c r="B47" t="n">
-        <v>78757</v>
+        <v>91357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>306585</v>
+        <v>306549</v>
       </c>
       <c r="R47" t="n">
-        <v>6523469</v>
+        <v>6523459</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,6 +5471,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5497,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113236967</v>
+        <v>113236893</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>78764</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5514,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>306533</v>
+        <v>306585</v>
       </c>
       <c r="R48" t="n">
-        <v>6523475</v>
+        <v>6523469</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5573,11 +5578,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>13 fruktkroppar</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 53705-2023 artfynd.xlsx
+++ b/artfynd/A 53705-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
